--- a/kb/out/FairRyde_KB_v0.2.xlsx
+++ b/kb/out/FairRyde_KB_v0.2.xlsx
@@ -610,7 +610,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>FairRyde_KB_v0.2.xlsx（本文件）：知识库，每次运行 build_kb.py 重新生成，不放任何标注。FairRyde_Annotation_v0.2.xlsx：标注工作簿，脚本只建一次；只要有人填过人工列，或文件正在 Excel 或 LibreOffice 里打开，脚本就不会覆盖它（ONT.11.3）。本次运行：FairRyde_Annotation_v0.2.xlsx 已生成（没有人工填写过），旧文件备份到 backup/FairRyde_Annotation_v0.2.20261014T115338.xlsx</t>
+          <t>FairRyde_KB_v0.2.xlsx（本文件）：知识库，每次运行 build_kb.py 重新生成，不放任何标注。FairRyde_Annotation_v0.2.xlsx：标注工作簿，脚本只建一次；只要有人填过人工列，或文件正在 Excel 或 LibreOffice 里打开，脚本就不会覆盖它（ONT.11.3）。本次运行：FairRyde_Annotation_v0.2.xlsx 已生成（没有人工填写过），旧文件备份到 backup/FairRyde_Annotation_v0.2.20261014T120616.xlsx</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>规则 90 条；逐字引文 148 条与原文一致，不符 0 条；DISP-002 的 59 个字段全部映射到本体；决策表 192 种输入组合每种恰好命中一行；引擎自测 125/125 通过；生成文件的隐私泄漏扫描命中 0 处；错误 0 个，警告 0 个。</t>
+          <t>规则 90 条；逐字引文 148 条与原文一致，不符 0 条；DISP-002 的 59 个字段全部映射到本体；决策表 192 种输入组合每种恰好命中一行；引擎自测 126/126 通过；生成文件的隐私泄漏扫描命中 0 处；错误 0 个，警告 0 个。</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>125 个单因素变体，检验规则卡与参考引擎一致（不是标准答案）</t>
+          <t>126 个单因素变体，检验规则卡与参考引擎一致（不是标准答案）</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="P46" s="5" t="inlineStr"/>
     </row>
-    <row r="47" ht="285.5" customHeight="1">
+    <row r="47" ht="312.5" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
           <t>CW-R08</t>
@@ -4104,12 +4104,12 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>乘客取消时司机已晚于派单 ETA 加宽限、或没有朝上车点移动（已在上车点等候的司机算作朝上车点移动），则乘客取消费可免除。Ryde 未公开此规则（通用假设）。预约单的派单 ETA 取预约时间（FairRyde 的读法：司机应在那时到达上车点）；但在 CW-R02 的截止时间之后才被接的预约单，派单 ETA 取接单时 App 给出的 ETA（若晚于预约时间）；预约单的司机没有移动时，只有按 App 从司机所在位置算的 ETA 已无法在派单 ETA 加宽限内到达上车点，才构成免除理由（提前到附近等候的司机不构成）。</t>
+          <t>乘客取消时司机已晚于派单 ETA 加宽限、或没有朝上车点移动（已在上车点等候的司机算作朝上车点移动），则乘客取消费可免除。Ryde 未公开此规则（通用假设）。预约单的派单 ETA 取预约时间（FairRyde 的读法：司机应在那时到达上车点）；但在 CW-R02 的截止时间之后才被接的预约单，派单 ETA 取接单时 App 给出的 ETA（若晚于预约时间）；预约单的司机没有移动时，只有按 App 从司机所在位置算的 ETA 已无法在派单 ETA 加宽限内到达上车点，才构成免除理由（提前到附近等候的司机不构成）。按本规则免除一律需人工批准（AUTH-02 第 13 项），不能自动。</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>If, when the rider canceled, the driver was already later than the assignment ETA plus DRIVER_LATE_GRACE_S, or was not moving toward the pick-up point (a driver already waiting at the pick-up counts as moving toward it), the rider's cancellation fee is eligible for a waiver. Ryde publishes no rule on this. For an advance booking the assignment ETA is the scheduled time (FairRyde's reading: the driver is due at the pick-up then), except for a request accepted after the cut-off of CW-R02, whose assignment ETA is the ETA the app gave at acceptance, if later than the scheduled time; and a driver who is not moving gives this ground only when, by the app's ETA from where the driver was, the driver could no longer reach the pick-up by the assignment ETA plus DRIVER_LATE_GRACE_S (an early driver waiting nearby is not a ground).</t>
+          <t>If, when the rider canceled, the driver was already later than the assignment ETA plus DRIVER_LATE_GRACE_S, or was not moving toward the pick-up point (a driver already waiting at the pick-up counts as moving toward it), the rider's cancellation fee is eligible for a waiver. Ryde publishes no rule on this. For an advance booking the assignment ETA is the scheduled time (FairRyde's reading: the driver is due at the pick-up then), except for a request accepted after the cut-off of CW-R02, whose assignment ETA is the ETA the app gave at acceptance, if later than the scheduled time; and a driver who is not moving gives this ground only when, by the app's ETA from where the driver was, the driver could no longer reach the pick-up by the assignment ETA plus DRIVER_LATE_GRACE_S (an early driver waiting nearby is not a ground). A waiver under this rule always needs human approval (AUTH-02 trigger 13), never AUTO.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -7324,12 +7324,12 @@
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>任一即需人工批准：有决定性的规则或决策表行；任何一方带欺诈信号（对称）；清洁费及所有"需批准"类型；金额超限或置信度不足；裁决所依赖的点存在已知来源矛盾（若矛盾会改变结果或金额，则按 META-04 转人工、按 AUTH-06 为 HUMAN）；对自动裁决的申诉；无联系记录、多收费用、记录缺失；决定性余量落在边界带内且各记录对起止时刻的差异大于余量（不论结果有利于谁）；维持收费而 pin 与场馆不符且乘客说自己在该场馆；结果有利的一方的文字里有注入指令；司机 GPS 无法确定等待期间是否离开（GPS_AMBIGUOUS，见 CW-F04B）；按是非曲直维持缺席取消费或等候费，而让司机算作已到达并在场的是 FairRyde 自己的 GPS 判断逻辑、不是定位点本身（CW-F04B：F-GPS-LOGIC 为真），或 CW-F04B 某个参数取其合理区间任一端时会如此（D29 把定位间隔和半径参数列入），决定 D29；缺席取消费的决策表行 R9、R11（可信度 D）本身已使其成为决定性的（decisive_definition 第 2、3 条），等候费没有决策表（D31），由这一项覆盖这两部分。</t>
+          <t>任一即需人工批准：有决定性的规则或决策表行；任何一方带欺诈信号（对称）；清洁费及所有"需批准"类型；金额超限或置信度不足；裁决所依赖的点存在已知来源矛盾（若矛盾会改变结果或金额，则按 META-04 转人工、按 AUTH-06 为 HUMAN）；对自动裁决的申诉；无联系记录、多收费用、记录缺失；决定性余量落在边界带内且各记录对起止时刻的差异大于余量（不论结果有利于谁）；维持收费而 pin 与场馆不符且乘客说自己在该场馆；结果有利的一方的文字里有注入指令；司机 GPS 无法确定等待期间是否离开（GPS_AMBIGUOUS，见 CW-F04B）；按是非曲直维持缺席取消费或等候费，而让司机算作已到达并在场的是 FairRyde 自己的 GPS 判断逻辑、不是定位点本身（CW-F04B：F-GPS-LOGIC 为真），或 CW-F04B 某个参数取其合理区间任一端时会如此（D29 把定位间隔和半径参数列入），决定 D29；缺席取消费的决策表行 R9、R11（可信度 D）本身已使其成为决定性的（decisive_definition 第 2、3 条），等候费没有决策表（D31），由这一项覆盖这两部分；因司机迟到或没有朝上车点移动而免除乘客取消费（CW-R08，可信度 D；CW-RIDERCANCEL 没有决策表，由这一项使免除需人工批准，与 D29 一致；Jasper，2026-10-14，待办 D40 (k)）。</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Human approval is required if any of these holds: (1) something is decisive (decisive_definition); (2) a FRAUD_SIGNAL on either party (symmetric, so history can never make one side's wins slower than its losses); (3) any cleaning claim, and every type with scope ADJUDICATE_WITH_APPROVAL; (4) amount above AUTO_LIMIT_SGD; confidence C below TAU; (5) a known source conflict (SOURCE_CONFLICT) on a point the ruling relies on, when FairRyde still reaches a ruling (a conflict that changes the outcome or the amount is ESCALATE_HUMAN under META-04, so tier HUMAN under AUTH-06); (6) an appeal of an automatic ruling; (7) CONTACT_NOT_ATTEMPTED; CHARGE_AMOUNT_MISMATCH with an overcharge; RECORDS_MISSING; (8) the decisive threshold margin is within BOUNDARY_BAND_S and the records disagree about the anchor or end time by more than the margin (MARGIN_WITHIN_SPREAD), whichever party the outcome favors; (9) the fee is upheld while PIN_VENUE_MISMATCH holds and the rider's statement places the rider at the named venue; (10) INJECTION_SUSPECTED in text from the party the proposed outcome favors; (11) GPS_AMBIGUOUS: the driver's GPS cannot settle whether the driver left during the wait (CW-F04B); (12) a no-show or waiting fee upheld on the merits while FairRyde's own GPS logic, and not the pings alone, makes the driver count as arrived and present (CW-F04B: F-GPS-LOGIC true), or would do so with one of CW-F04B's parameters at either end of its plausible range (D29 names the ping-gap and radius parameters), decision D29. For a no-show fee the decision-table rows R9 and R11 (rated D) already make it decisive (decisive_definition clauses 2 and 3); a waiting fee has no decision table (D31), so this trigger carries both parts.</t>
+          <t>Human approval is required if any of these holds: (1) something is decisive (decisive_definition); (2) a FRAUD_SIGNAL on either party (symmetric, so history can never make one side's wins slower than its losses); (3) any cleaning claim, and every type with scope ADJUDICATE_WITH_APPROVAL; (4) amount above AUTO_LIMIT_SGD; confidence C below TAU; (5) a known source conflict (SOURCE_CONFLICT) on a point the ruling relies on, when FairRyde still reaches a ruling (a conflict that changes the outcome or the amount is ESCALATE_HUMAN under META-04, so tier HUMAN under AUTH-06); (6) an appeal of an automatic ruling; (7) CONTACT_NOT_ATTEMPTED; CHARGE_AMOUNT_MISMATCH with an overcharge; RECORDS_MISSING; (8) the decisive threshold margin is within BOUNDARY_BAND_S and the records disagree about the anchor or end time by more than the margin (MARGIN_WITHIN_SPREAD), whichever party the outcome favors; (9) the fee is upheld while PIN_VENUE_MISMATCH holds and the rider's statement places the rider at the named venue; (10) INJECTION_SUSPECTED in text from the party the proposed outcome favors; (11) GPS_AMBIGUOUS: the driver's GPS cannot settle whether the driver left during the wait (CW-F04B); (12) a no-show or waiting fee upheld on the merits while FairRyde's own GPS logic, and not the pings alone, makes the driver count as arrived and present (CW-F04B: F-GPS-LOGIC true), or would do so with one of CW-F04B's parameters at either end of its plausible range (D29 names the ping-gap and radius parameters), decision D29. For a no-show fee the decision-table rows R9 and R11 (rated D) already make it decisive (decisive_definition clauses 2 and 3); a waiting fee has no decision table (D31), so this trigger carries both parts; (13) a rider's cancellation fee waived because the driver was late or not moving toward the pick-up (CW-R08, rated D; CW-RIDERCANCEL has no decision table, so this trigger makes the waiver need approval, in line with D29; Jasper, 2026-10-14, open item D40 (k)).</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="L43" s="2" t="n"/>
     </row>
-    <row r="44" ht="42.5" customHeight="1">
+    <row r="44" ht="272" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
           <t>shared</t>
@@ -10951,7 +10951,7 @@
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
@@ -10961,12 +10961,12 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>10; 100</t>
+          <t>20; 100</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>The organizer's own auto-arrival check uses 10 m (lower end); 50 m allows for GPS error near tall buildings.</t>
+          <t>50 m allows for GPS error near tall buildings. The low end of the plausible range is 20 m (Jasper, 2026-10-14, open item D39 (g)): it sits above ordinary phone GPS error, so jitter around a parked car does not count as being away at the low end. Reasons: GPS-enabled smartphones are typically accurate to about 4.9 m under open sky and worse near buildings, bridges and trees (gps.gov, 'GPS Accuracy'); a smartphone study in a Hong Kong urban canyon, a dense high-rise setting, reports a mean error of about 14.5 m for standard positioning (arXiv 2109.00683, 'Time-correlated Window Carrier-phase Aided GNSS Positioning Using Factor Graph Optimization for Urban Positioning'). Both are paraphrased from search results: the pages could not be fetched from the build environment, so they are not in kb/sources. The organizer's auto-arrival check uses 10 m ('Driver GPS within 10m of pickup point.'), below that error, so it was the low end only until 2026-10-14. FairRyde's choice, D.</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Driver lateness (generic assumption: other platforms' practice; FairRyde's condition for a driver not moving toward the pick-up and FairRyde's reading of an advance booking's assignment ETA; credibility D)</t>
+          <t>Driver lateness (generic assumption: other platforms' practice; FairRyde's condition for a driver not moving toward the pick-up and FairRyde's reading of an advance booking's assignment ETA; credibility D); a waiver always needs approval (AUTH-02 trigger 13)</t>
         </is>
       </c>
     </row>
@@ -16002,12 +16002,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>任一即需人工批准：有决定性的规则或决策表行；任何一方带欺诈信号（对称）；清洁费及所有"需批准"类型；金额超限或置信度不足；裁决所依赖的点存在已知来源矛盾（若矛盾会改变结果或金额，则按 META-04 转人工、按 AUTH-06 为 HUMAN）；对自动裁决的申诉；无联系记录、多收费用、记录缺失；决定性余量落在边界带内且各记录对起止时刻的差异大于余量（不论结果有利于谁）；维持收费而 pin 与场馆不符且乘客说自己在该场馆；结果有利的一方的文字里有注入指令；司机 GPS 无法确定等待期间是否离开（GPS_AMBIGUOUS，见 CW-F04B）；按是非曲直维持缺席取消费或等候费，而让司机算作已到达并在场的是 FairRyde 自己的 GPS 判断逻辑、不是定位点本身（CW-F04B：F-GPS-LOGIC 为真），或 CW-F04B 某个参数取其合理区间任一端时会如此（D29 把定位间隔和半径参数列入），决定 D29；缺席取消费的决策表行 R9、R11（可信度 D）本身已使其成为决定性的（decisive_definition 第 2、3 条），等候费没有决策表（D31），由这一项覆盖这两部分。</t>
+          <t>任一即需人工批准：有决定性的规则或决策表行；任何一方带欺诈信号（对称）；清洁费及所有"需批准"类型；金额超限或置信度不足；裁决所依赖的点存在已知来源矛盾（若矛盾会改变结果或金额，则按 META-04 转人工、按 AUTH-06 为 HUMAN）；对自动裁决的申诉；无联系记录、多收费用、记录缺失；决定性余量落在边界带内且各记录对起止时刻的差异大于余量（不论结果有利于谁）；维持收费而 pin 与场馆不符且乘客说自己在该场馆；结果有利的一方的文字里有注入指令；司机 GPS 无法确定等待期间是否离开（GPS_AMBIGUOUS，见 CW-F04B）；按是非曲直维持缺席取消费或等候费，而让司机算作已到达并在场的是 FairRyde 自己的 GPS 判断逻辑、不是定位点本身（CW-F04B：F-GPS-LOGIC 为真），或 CW-F04B 某个参数取其合理区间任一端时会如此（D29 把定位间隔和半径参数列入），决定 D29；缺席取消费的决策表行 R9、R11（可信度 D）本身已使其成为决定性的（decisive_definition 第 2、3 条），等候费没有决策表（D31），由这一项覆盖这两部分；因司机迟到或没有朝上车点移动而免除乘客取消费（CW-R08，可信度 D；CW-RIDERCANCEL 没有决策表，由这一项使免除需人工批准，与 D29 一致；Jasper，2026-10-14，待办 D40 (k)）。</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Human approval is required if any of these holds: (1) something is decisive (decisive_definition); (2) a FRAUD_SIGNAL on either party (symmetric, so history can never make one side's wins slower than its losses); (3) any cleaning claim, and every type with scope ADJUDICATE_WITH_APPROVAL; (4) amount above AUTO_LIMIT_SGD; confidence C below TAU; (5) a known source conflict (SOURCE_CONFLICT) on a point the ruling relies on, when FairRyde still reaches a ruling (a conflict that changes the outcome or the amount is ESCALATE_HUMAN under META-04, so tier HUMAN under AUTH-06); (6) an appeal of an automatic ruling; (7) CONTACT_NOT_ATTEMPTED; CHARGE_AMOUNT_MISMATCH with an overcharge; RECORDS_MISSING; (8) the decisive threshold margin is within BOUNDARY_BAND_S and the records disagree about the anchor or end time by more than the margin (MARGIN_WITHIN_SPREAD), whichever party the outcome favors; (9) the fee is upheld while PIN_VENUE_MISMATCH holds and the rider's statement places the rider at the named venue; (10) INJECTION_SUSPECTED in text from the party the proposed outcome favors; (11) GPS_AMBIGUOUS: the driver's GPS cannot settle whether the driver left during the wait (CW-F04B); (12) a no-show or waiting fee upheld on the merits while FairRyde's own GPS logic, and not the pings alone, makes the driver count as arrived and present (CW-F04B: F-GPS-LOGIC true), or would do so with one of CW-F04B's parameters at either end of its plausible range (D29 names the ping-gap and radius parameters), decision D29. For a no-show fee the decision-table rows R9 and R11 (rated D) already make it decisive (decisive_definition clauses 2 and 3); a waiting fee has no decision table (D31), so this trigger carries both parts.</t>
+          <t>Human approval is required if any of these holds: (1) something is decisive (decisive_definition); (2) a FRAUD_SIGNAL on either party (symmetric, so history can never make one side's wins slower than its losses); (3) any cleaning claim, and every type with scope ADJUDICATE_WITH_APPROVAL; (4) amount above AUTO_LIMIT_SGD; confidence C below TAU; (5) a known source conflict (SOURCE_CONFLICT) on a point the ruling relies on, when FairRyde still reaches a ruling (a conflict that changes the outcome or the amount is ESCALATE_HUMAN under META-04, so tier HUMAN under AUTH-06); (6) an appeal of an automatic ruling; (7) CONTACT_NOT_ATTEMPTED; CHARGE_AMOUNT_MISMATCH with an overcharge; RECORDS_MISSING; (8) the decisive threshold margin is within BOUNDARY_BAND_S and the records disagree about the anchor or end time by more than the margin (MARGIN_WITHIN_SPREAD), whichever party the outcome favors; (9) the fee is upheld while PIN_VENUE_MISMATCH holds and the rider's statement places the rider at the named venue; (10) INJECTION_SUSPECTED in text from the party the proposed outcome favors; (11) GPS_AMBIGUOUS: the driver's GPS cannot settle whether the driver left during the wait (CW-F04B); (12) a no-show or waiting fee upheld on the merits while FairRyde's own GPS logic, and not the pings alone, makes the driver count as arrived and present (CW-F04B: F-GPS-LOGIC true), or would do so with one of CW-F04B's parameters at either end of its plausible range (D29 names the ping-gap and radius parameters), decision D29. For a no-show fee the decision-table rows R9 and R11 (rated D) already make it decisive (decisive_definition clauses 2 and 3); a waiting fee has no decision table (D31), so this trigger carries both parts; (13) a rider's cancellation fee waived because the driver was late or not moving toward the pick-up (CW-R08, rated D; CW-RIDERCANCEL has no decision table, so this trigger makes the waiver need approval, in line with D29; Jasper, 2026-10-14, open item D40 (k)).</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -20992,12 +20992,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>50 · [10, 100] · D</t>
+          <t>50 · [20, 100] · D</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>10 -&gt; UPHOLD (R8)</t>
+          <t>20 -&gt; UPHOLD (R8)</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -21798,7 +21798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I131"/>
+  <dimension ref="A1:I132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -24010,7 +24010,7 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>decisive: CW-F03B (the other reading (wait counted from the anchor, regardless of GPS) gives UPHOLD); CW-R06 (outcome changes when TS_TOLERANCE_S moves within [5, 60]); CW-F04B (outcome changes when TS_TOLERANCE_S moves within [5, 60]); CW-F06 (outcome changes when TS_TOLERANCE_S moves within [5, 60]); CW-F04B (outcome changes when ARRIVAL_GEOFENCE_M moves within [10, 100]); fraud signal on RIDER (3 of 4 past disputes rejected; platform flag: flagged_for_frequent_late_cancellations) (symmetric trigger; the detail is for the reviewer, not for the parties)</t>
+          <t>decisive: CW-F03B (the other reading (wait counted from the anchor, regardless of GPS) gives UPHOLD); CW-R06 (outcome changes when TS_TOLERANCE_S moves within [5, 60]); CW-F04B (outcome changes when TS_TOLERANCE_S moves within [5, 60]); CW-F06 (outcome changes when TS_TOLERANCE_S moves within [5, 60]); CW-F04B (outcome changes when ARRIVAL_GEOFENCE_M moves within [20, 100]); fraud signal on RIDER (3 of 4 past disputes rejected; platform flag: flagged_for_frequent_late_cancellations) (symmetric trigger; the detail is for the reviewer, not for the parties)</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr"/>
@@ -26198,7 +26198,7 @@
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>V06 with pings 3 m from the pin and one 15 m away: inside the 50 m area, but at the radius's 10 m low end it is an outlier, so the uphold would rest on FairRyde's logic (D29, radius part): approval</t>
+          <t>V06 with pings 3 m from the pin and one 25 m away: inside the 50 m area, but at the radius's 20 m low end it is an outlier, so the uphold would rest on FairRyde's logic (D29, radius part): approval</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
@@ -26223,7 +26223,7 @@
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>decisive: CW-F04B (the ruling would rest on a decision-table row rated C or D when ARRIVAL_GEOFENCE_M moves within [10, 100]); fee upheld, and FairRyde's own GPS logic would decide it with ARRIVAL_GEOFENCE_M at an end of its plausible range (CW-F04B, D29)</t>
+          <t>decisive: CW-F04B (the ruling would rest on a decision-table row rated C or D when ARRIVAL_GEOFENCE_M moves within [20, 100]); fee upheld, and FairRyde's own GPS logic would decide it with ARRIVAL_GEOFENCE_M at an end of its plausible range (CW-F04B, D29)</t>
         </is>
       </c>
       <c r="H111" s="7" t="inlineStr"/>
@@ -26233,42 +26233,34 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="96.5" customHeight="1">
+    <row r="112" ht="83" customHeight="1">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>V101</t>
+          <t>V99B</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>Ryde advance booking for 08:45 with the platform check at 08:38; an outlier 10 s after the indication is the last ping before 08:38:30, so without the logic it would contradict the check: R11 (D29)</t>
+          <t>as V99 with the far ping 15 m away: ordinary GPS error, inside the radius even at its 20 m low end (Jasper, 2026-10-14, D39 (g)), so the uphold rests on the pings alone: automatic</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>outcome: UPHOLD; row: R11; tier: APPROVE; profile: ryde_2026; findings: F-GPS-LOGIC: 是</t>
+          <t>outcome: UPHOLD; row: R8; tier: AUTO; findings: F-GPS-LOGIC: 否; not_decisive: CW-F04B; not_triggers: D29</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>outcome: UPHOLD; row: R11; tier: APPROVE; reasons: CW-R-NOSHOW-VALID; profile: ryde_2026; C: 0.964</t>
+          <t>outcome: UPHOLD; row: R8; tier: AUTO; reasons: CW-R-NOSHOW-VALID; profile: organizer_case; C: 0.964</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>NO_RIDER_EVIDENCE; CHARGE_AMOUNT_MISMATCH; GENERIC_ASSUMPTION_USED</t>
-        </is>
-      </c>
-      <c r="F112" s="7" t="inlineStr">
-        <is>
-          <t>DT-CW-NOSHOW R11</t>
-        </is>
-      </c>
-      <c r="G112" s="7" t="inlineStr">
-        <is>
-          <t>decisive: DT-CW-NOSHOW R11 (decision-table row rated D); fee upheld on FairRyde's own GPS logic, not on the pings alone (CW-F04B, D29)</t>
-        </is>
-      </c>
+          <t>BOOKING_TYPE_INFERRED; NO_RIDER_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr"/>
+      <c r="G112" s="7" t="inlineStr"/>
       <c r="H112" s="7" t="inlineStr"/>
       <c r="I112" s="7" t="inlineStr">
         <is>
@@ -26276,30 +26268,30 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="83" customHeight="1">
+    <row r="113" ht="96.5" customHeight="1">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>V102</t>
+          <t>V101</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>Ryde on-demand trip: at the pin until 08:45:00, then the next ping (08:46:40, 400 m) comes 40 s after the 3-minute wait ended: the driver may have left before it ended, so approval</t>
+          <t>Ryde advance booking for 08:45 with the platform check at 08:38; an outlier 10 s after the indication is the last ping before 08:38:30, so without the logic it would contradict the check: R11 (D29)</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>outcome: UPHOLD; row: R11; profile: ryde_2026; tier: APPROVE; flags: GPS_AMBIGUOUS; triggers: D29</t>
+          <t>outcome: UPHOLD; row: R11; tier: APPROVE; profile: ryde_2026; findings: F-GPS-LOGIC: 是</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>outcome: UPHOLD; row: R11; tier: APPROVE; reasons: CW-R-NOSHOW-VALID; profile: ryde_2026; C: 1.0</t>
+          <t>outcome: UPHOLD; row: R11; tier: APPROVE; reasons: CW-R-NOSHOW-VALID; profile: ryde_2026; C: 0.964</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>GPS_AMBIGUOUS; NO_RIDER_EVIDENCE; CHARGE_AMOUNT_MISMATCH; GENERIC_ASSUMPTION_USED</t>
+          <t>NO_RIDER_EVIDENCE; CHARGE_AMOUNT_MISMATCH; GENERIC_ASSUMPTION_USED</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
@@ -26309,7 +26301,7 @@
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>decisive: DT-CW-NOSHOW R11 (decision-table row rated D); GPS cannot settle whether the driver left (GPS_AMBIGUOUS); fee upheld on FairRyde's own GPS logic, not on the pings alone (CW-F04B, D29)</t>
+          <t>decisive: DT-CW-NOSHOW R11 (decision-table row rated D); fee upheld on FairRyde's own GPS logic, not on the pings alone (CW-F04B, D29)</t>
         </is>
       </c>
       <c r="H113" s="7" t="inlineStr"/>
@@ -26319,92 +26311,88 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="96.5" customHeight="1">
+    <row r="114" ht="83" customHeight="1">
       <c r="A114" s="7" t="inlineStr">
         <is>
+          <t>V102</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>Ryde on-demand trip: at the pin until 08:45:00, then the next ping (08:46:40, 400 m) comes 40 s after the 3-minute wait ended: the driver may have left before it ended, so approval</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>outcome: UPHOLD; row: R11; profile: ryde_2026; tier: APPROVE; flags: GPS_AMBIGUOUS; triggers: D29</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>outcome: UPHOLD; row: R11; tier: APPROVE; reasons: CW-R-NOSHOW-VALID; profile: ryde_2026; C: 1.0</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>GPS_AMBIGUOUS; NO_RIDER_EVIDENCE; CHARGE_AMOUNT_MISMATCH; GENERIC_ASSUMPTION_USED</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>DT-CW-NOSHOW R11</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>decisive: DT-CW-NOSHOW R11 (decision-table row rated D); GPS cannot settle whether the driver left (GPS_AMBIGUOUS); fee upheld on FairRyde's own GPS logic, not on the pings alone (CW-F04B, D29)</t>
+        </is>
+      </c>
+      <c r="H114" s="7" t="inlineStr"/>
+      <c r="I114" s="7" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="96.5" customHeight="1">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
           <t>V103</t>
         </is>
       </c>
-      <c r="B114" s="7" t="inlineStr">
+      <c r="B115" s="7" t="inlineStr">
         <is>
           <t>Ryde advance booking for 08:45: 400 m away from 08:40:20 to 08:44:50 and first back at the pin at 08:45:50: the pings cannot show the driver at the pick-up when the counted wait started, so approval</t>
         </is>
       </c>
-      <c r="C114" s="7" t="inlineStr">
+      <c r="C115" s="7" t="inlineStr">
         <is>
           <t>outcome: UPHOLD; row: R11; profile: ryde_2026; tier: APPROVE; flags: GPS_AMBIGUOUS; triggers: D29</t>
         </is>
       </c>
-      <c r="D114" s="7" t="inlineStr">
+      <c r="D115" s="7" t="inlineStr">
         <is>
           <t>outcome: UPHOLD; row: R11; tier: APPROVE; reasons: CW-R-NOSHOW-VALID; profile: ryde_2026; C: 0.767</t>
         </is>
       </c>
-      <c r="E114" s="7" t="inlineStr">
+      <c r="E115" s="7" t="inlineStr">
         <is>
           <t>TIMER_ANCHOR_MISMATCH; BOUNDARY_MARGIN; MARGIN_WITHIN_SPREAD; GPS_AMBIGUOUS; NO_RIDER_EVIDENCE; CHARGE_AMOUNT_MISMATCH; GENERIC_ASSUMPTION_USED</t>
         </is>
       </c>
-      <c r="F114" s="7" t="inlineStr">
+      <c r="F115" s="7" t="inlineStr">
         <is>
           <t>DT-CW-NOSHOW R11</t>
         </is>
       </c>
-      <c r="G114" s="7" t="inlineStr">
+      <c r="G115" s="7" t="inlineStr">
         <is>
           <t>decisive: DT-CW-NOSHOW R11 (decision-table row rated D); GPS cannot settle whether the driver left (GPS_AMBIGUOUS); fee upheld on FairRyde's own GPS logic, not on the pings alone (CW-F04B, D29); margin +10 s within the boundary band, and the records disagree by up to 490 s</t>
         </is>
       </c>
-      <c r="H114" s="7" t="inlineStr">
+      <c r="H115" s="7" t="inlineStr">
         <is>
           <t>G1 data inconsistency</t>
-        </is>
-      </c>
-      <c r="I114" s="7" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="191" customHeight="1">
-      <c r="A115" s="7" t="inlineStr">
-        <is>
-          <t>V104</t>
-        </is>
-      </c>
-      <c r="B115" s="7" t="inlineStr">
-        <is>
-          <t>safety content without v0.1's words in the description: 'After that he stopped on the PIE and told me to get out of the car.'</t>
-        </is>
-      </c>
-      <c r="C115" s="7" t="inlineStr">
-        <is>
-          <t>tier: HUMAN; gates: G4</t>
-        </is>
-      </c>
-      <c r="D115" s="7" t="inlineStr">
-        <is>
-          <t>outcome: UPHOLD; row: R8; tier: HUMAN; reasons: CW-R-NOSHOW-VALID; CW-R-PIN-AMBIGUOUS; profile: organizer_case; C: 0.689</t>
-        </is>
-      </c>
-      <c r="E115" s="7" t="inlineStr">
-        <is>
-          <t>BOOKING_TYPE_INFERRED; BOUNDARY_MARGIN; MARGIN_WITHIN_SPREAD; NO_RIDER_EVIDENCE; PIN_VENUE_MISMATCH; FRAUD_SIGNAL; GENERIC_ASSUMPTION_USED</t>
-        </is>
-      </c>
-      <c r="F115" s="7" t="inlineStr">
-        <is>
-          <t>CW-F04B</t>
-        </is>
-      </c>
-      <c r="G115" s="7" t="inlineStr">
-        <is>
-          <t>decisive: CW-F04B (outcome changes when PING_MAX_GAP_S moves within [60, 420]); fraud signal on RIDER (3 of 4 past disputes rejected; platform flag: flagged_for_frequent_late_cancellations) (symmetric trigger; the detail is for the reviewer, not for the parties); fee upheld, and FairRyde's own GPS logic would decide it with PING_MAX_GAP_S at an end of its plausible range (CW-F04B, D29); margin +0 s within the boundary band, and the records disagree by up to 10 s; fee upheld, pin far from Tiong Bahru Plaza and the rider says they were there</t>
-        </is>
-      </c>
-      <c r="H115" s="7" t="inlineStr">
-        <is>
-          <t>G4 safety content</t>
         </is>
       </c>
       <c r="I115" s="7" t="inlineStr">
@@ -26416,12 +26404,12 @@
     <row r="116" ht="191" customHeight="1">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>V105</t>
+          <t>V104</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>safety content without v0.1's words in the description: 'He then drove the wrong way and would not let me out, I felt kidnapped.'</t>
+          <t>safety content without v0.1's words in the description: 'After that he stopped on the PIE and told me to get out of the car.'</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
@@ -26463,12 +26451,12 @@
     <row r="117" ht="191" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>V106</t>
+          <t>V105</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>safety content without v0.1's words in the description: 'He made racist remarks about me.'</t>
+          <t>safety content without v0.1's words in the description: 'He then drove the wrong way and would not let me out, I felt kidnapped.'</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
@@ -26510,70 +26498,86 @@
     <row r="118" ht="191" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
         <is>
+          <t>V106</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>safety content without v0.1's words in the description: 'He made racist remarks about me.'</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>tier: HUMAN; gates: G4</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>outcome: UPHOLD; row: R8; tier: HUMAN; reasons: CW-R-NOSHOW-VALID; CW-R-PIN-AMBIGUOUS; profile: organizer_case; C: 0.689</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>BOOKING_TYPE_INFERRED; BOUNDARY_MARGIN; MARGIN_WITHIN_SPREAD; NO_RIDER_EVIDENCE; PIN_VENUE_MISMATCH; FRAUD_SIGNAL; GENERIC_ASSUMPTION_USED</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>CW-F04B</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>decisive: CW-F04B (outcome changes when PING_MAX_GAP_S moves within [60, 420]); fraud signal on RIDER (3 of 4 past disputes rejected; platform flag: flagged_for_frequent_late_cancellations) (symmetric trigger; the detail is for the reviewer, not for the parties); fee upheld, and FairRyde's own GPS logic would decide it with PING_MAX_GAP_S at an end of its plausible range (CW-F04B, D29); margin +0 s within the boundary band, and the records disagree by up to 10 s; fee upheld, pin far from Tiong Bahru Plaza and the rider says they were there</t>
+        </is>
+      </c>
+      <c r="H118" s="7" t="inlineStr">
+        <is>
+          <t>G4 safety content</t>
+        </is>
+      </c>
+      <c r="I118" s="7" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="191" customHeight="1">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
           <t>V107</t>
         </is>
       </c>
-      <c r="B118" s="7" t="inlineStr">
+      <c r="B119" s="7" t="inlineStr">
         <is>
           <t>rudeness alone in the description: not safety content, the no-show ruling stands as for DISP-002</t>
         </is>
       </c>
-      <c r="C118" s="7" t="inlineStr">
+      <c r="C119" s="7" t="inlineStr">
         <is>
           <t>outcome: UPHOLD; row: R8; tier: APPROVE; not_gates: G4</t>
         </is>
       </c>
-      <c r="D118" s="7" t="inlineStr">
+      <c r="D119" s="7" t="inlineStr">
         <is>
           <t>outcome: UPHOLD; row: R8; tier: APPROVE; reasons: CW-R-NOSHOW-VALID; CW-R-PIN-AMBIGUOUS; profile: organizer_case; C: 0.689</t>
         </is>
       </c>
-      <c r="E118" s="7" t="inlineStr">
+      <c r="E119" s="7" t="inlineStr">
         <is>
           <t>BOOKING_TYPE_INFERRED; BOUNDARY_MARGIN; MARGIN_WITHIN_SPREAD; NO_RIDER_EVIDENCE; PIN_VENUE_MISMATCH; FRAUD_SIGNAL; GENERIC_ASSUMPTION_USED</t>
         </is>
       </c>
-      <c r="F118" s="7" t="inlineStr">
+      <c r="F119" s="7" t="inlineStr">
         <is>
           <t>CW-F04B</t>
         </is>
       </c>
-      <c r="G118" s="7" t="inlineStr">
+      <c r="G119" s="7" t="inlineStr">
         <is>
           <t>decisive: CW-F04B (outcome changes when PING_MAX_GAP_S moves within [60, 420]); fraud signal on RIDER (3 of 4 past disputes rejected; platform flag: flagged_for_frequent_late_cancellations) (symmetric trigger; the detail is for the reviewer, not for the parties); fee upheld, and FairRyde's own GPS logic would decide it with PING_MAX_GAP_S at an end of its plausible range (CW-F04B, D29); margin +0 s within the boundary band, and the records disagree by up to 10 s; fee upheld, pin far from Tiong Bahru Plaza and the rider says they were there</t>
         </is>
       </c>
-      <c r="H118" s="7" t="inlineStr"/>
-      <c r="I118" s="7" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="56" customHeight="1">
-      <c r="A119" s="7" t="inlineStr">
-        <is>
-          <t>V108</t>
-        </is>
-      </c>
-      <c r="B119" s="7" t="inlineStr">
-        <is>
-          <t>every record says the rider canceled: a rider cancellation fee case (CW-RIDERCANCEL), not ruled here</t>
-        </is>
-      </c>
-      <c r="C119" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reclassified: CW-RIDERCANCEL; outcome: </t>
-        </is>
-      </c>
-      <c r="D119" s="7" t="inlineStr">
-        <is>
-          <t>tier: n/a (reclassified to CW-RIDERCANCEL); reasons: ; profile: organizer_case; reclassified: CW-RIDERCANCEL</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="inlineStr"/>
-      <c r="F119" s="7" t="inlineStr"/>
-      <c r="G119" s="7" t="inlineStr"/>
       <c r="H119" s="7" t="inlineStr"/>
       <c r="I119" s="7" t="inlineStr">
         <is>
@@ -26584,31 +26588,27 @@
     <row r="120" ht="56" customHeight="1">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>V109</t>
+          <t>V108</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>reason rider_no_show, but the app events record a rider cancellation: the records disagree (CLS-06)</t>
+          <t>every record says the rider canceled: a rider cancellation fee case (CW-RIDERCANCEL), not ruled here</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>outcome: REQUEST_INFO; reasons: GEN-R-NEED-INFO; tier: HUMAN</t>
+          <t xml:space="preserve">reclassified: CW-RIDERCANCEL; outcome: </t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>outcome: REQUEST_INFO; tier: HUMAN; reasons: GEN-R-NEED-INFO; profile: organizer_case</t>
+          <t>tier: n/a (reclassified to CW-RIDERCANCEL); reasons: ; profile: organizer_case; reclassified: CW-RIDERCANCEL</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr"/>
       <c r="F120" s="7" t="inlineStr"/>
-      <c r="G120" s="7" t="inlineStr">
-        <is>
-          <t>who canceled is not settled by the trip record, so no fee ruling is made until it is (CLS-06)</t>
-        </is>
-      </c>
+      <c r="G120" s="7" t="inlineStr"/>
       <c r="H120" s="7" t="inlineStr"/>
       <c r="I120" s="7" t="inlineStr">
         <is>
@@ -26616,15 +26616,15 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="42.5" customHeight="1">
+    <row r="121" ht="56" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>V110</t>
+          <t>V109</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>no record says who canceled: ask for the trip record, no fee ruling (CLS-06)</t>
+          <t>reason rider_no_show, but the app events record a rider cancellation: the records disagree (CLS-06)</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
@@ -26654,27 +26654,31 @@
     <row r="122" ht="42.5" customHeight="1">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>V111</t>
+          <t>V110</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>the driver canceled for another reason (driver_cancelled_other): not a no-show, CW-OTHER (CLS-06)</t>
+          <t>no record says who canceled: ask for the trip record, no fee ruling (CLS-06)</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>reclassified: CW-OTHER</t>
+          <t>outcome: REQUEST_INFO; reasons: GEN-R-NEED-INFO; tier: HUMAN</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>tier: n/a (reclassified to CW-OTHER); reasons: ; profile: organizer_case; reclassified: CW-OTHER</t>
+          <t>outcome: REQUEST_INFO; tier: HUMAN; reasons: GEN-R-NEED-INFO; profile: organizer_case</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr"/>
       <c r="F122" s="7" t="inlineStr"/>
-      <c r="G122" s="7" t="inlineStr"/>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>who canceled is not settled by the trip record, so no fee ruling is made until it is (CLS-06)</t>
+        </is>
+      </c>
       <c r="H122" s="7" t="inlineStr"/>
       <c r="I122" s="7" t="inlineStr">
         <is>
@@ -26682,70 +26686,66 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="56" customHeight="1">
+    <row r="123" ht="42.5" customHeight="1">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>V112</t>
+          <t>V111</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>a rider cancellation with safety content: reclassified, and still a person sees it (CLS-01, gate G4)</t>
+          <t>the driver canceled for another reason (driver_cancelled_other): not a no-show, CW-OTHER (CLS-06)</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>reclassified: CW-RIDERCANCEL; tier: HUMAN; gates: G4</t>
+          <t>reclassified: CW-OTHER</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>tier: HUMAN; reasons: ; profile: organizer_case; reclassified: CW-RIDERCANCEL</t>
+          <t>tier: n/a (reclassified to CW-OTHER); reasons: ; profile: organizer_case; reclassified: CW-OTHER</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr"/>
       <c r="F123" s="7" t="inlineStr"/>
       <c r="G123" s="7" t="inlineStr"/>
-      <c r="H123" s="7" t="inlineStr">
-        <is>
-          <t>G4 safety content</t>
-        </is>
-      </c>
+      <c r="H123" s="7" t="inlineStr"/>
       <c r="I123" s="7" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="42.5" customHeight="1">
+    <row r="124" ht="56" customHeight="1">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>V113</t>
+          <t>V112</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>cancelled_by 'customer' against reason rider_no_show: the records disagree (CLS-06)</t>
+          <t>a rider cancellation with safety content: reclassified, and still a person sees it (CLS-01, gate G4)</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>outcome: REQUEST_INFO; reasons: GEN-R-NEED-INFO; tier: HUMAN</t>
+          <t>reclassified: CW-RIDERCANCEL; tier: HUMAN; gates: G4</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>outcome: REQUEST_INFO; tier: HUMAN; reasons: GEN-R-NEED-INFO; profile: organizer_case</t>
+          <t>tier: HUMAN; reasons: ; profile: organizer_case; reclassified: CW-RIDERCANCEL</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr"/>
       <c r="F124" s="7" t="inlineStr"/>
-      <c r="G124" s="7" t="inlineStr">
-        <is>
-          <t>who canceled is not settled by the trip record, so no fee ruling is made until it is (CLS-06)</t>
-        </is>
-      </c>
-      <c r="H124" s="7" t="inlineStr"/>
+      <c r="G124" s="7" t="inlineStr"/>
+      <c r="H124" s="7" t="inlineStr">
+        <is>
+          <t>G4 safety content</t>
+        </is>
+      </c>
       <c r="I124" s="7" t="inlineStr">
         <is>
           <t>通过</t>
@@ -26755,12 +26755,12 @@
     <row r="125" ht="42.5" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>V114</t>
+          <t>V113</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>an app event spelled rider_canceled against reason rider_no_show: the records disagree</t>
+          <t>cancelled_by 'customer' against reason rider_no_show: the records disagree (CLS-06)</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
@@ -26790,12 +26790,12 @@
     <row r="126" ht="42.5" customHeight="1">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>V115</t>
+          <t>V114</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>a system message 'Trip auto-cancelled' against reason rider_no_show: the records disagree</t>
+          <t>an app event spelled rider_canceled against reason rider_no_show: the records disagree</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
@@ -26825,27 +26825,31 @@
     <row r="127" ht="42.5" customHeight="1">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>V116</t>
+          <t>V115</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>the system canceled and the record gives no reason: CW-OTHER (CLS-06)</t>
+          <t>a system message 'Trip auto-cancelled' against reason rider_no_show: the records disagree</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>reclassified: CW-OTHER</t>
+          <t>outcome: REQUEST_INFO; reasons: GEN-R-NEED-INFO; tier: HUMAN</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>tier: n/a (reclassified to CW-OTHER); reasons: ; profile: organizer_case; reclassified: CW-OTHER</t>
+          <t>outcome: REQUEST_INFO; tier: HUMAN; reasons: GEN-R-NEED-INFO; profile: organizer_case</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr"/>
       <c r="F127" s="7" t="inlineStr"/>
-      <c r="G127" s="7" t="inlineStr"/>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>who canceled is not settled by the trip record, so no fee ruling is made until it is (CLS-06)</t>
+        </is>
+      </c>
       <c r="H127" s="7" t="inlineStr"/>
       <c r="I127" s="7" t="inlineStr">
         <is>
@@ -26853,42 +26857,30 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="191" customHeight="1">
+    <row r="128" ht="42.5" customHeight="1">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>V117</t>
+          <t>V116</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>the reason written RIDER_NO_SHOW is still a driver's no-show cancellation: as DISP-002</t>
+          <t>the system canceled and the record gives no reason: CW-OTHER (CLS-06)</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>outcome: UPHOLD; row: R8; tier: APPROVE</t>
+          <t>reclassified: CW-OTHER</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>outcome: UPHOLD; row: R8; tier: APPROVE; reasons: CW-R-NOSHOW-VALID; CW-R-PIN-AMBIGUOUS; profile: organizer_case; C: 0.689</t>
-        </is>
-      </c>
-      <c r="E128" s="7" t="inlineStr">
-        <is>
-          <t>BOOKING_TYPE_INFERRED; BOUNDARY_MARGIN; MARGIN_WITHIN_SPREAD; NO_RIDER_EVIDENCE; PIN_VENUE_MISMATCH; FRAUD_SIGNAL; GENERIC_ASSUMPTION_USED</t>
-        </is>
-      </c>
-      <c r="F128" s="7" t="inlineStr">
-        <is>
-          <t>CW-F04B</t>
-        </is>
-      </c>
-      <c r="G128" s="7" t="inlineStr">
-        <is>
-          <t>decisive: CW-F04B (outcome changes when PING_MAX_GAP_S moves within [60, 420]); fraud signal on RIDER (3 of 4 past disputes rejected; platform flag: flagged_for_frequent_late_cancellations) (symmetric trigger; the detail is for the reviewer, not for the parties); fee upheld, and FairRyde's own GPS logic would decide it with PING_MAX_GAP_S at an end of its plausible range (CW-F04B, D29); margin +0 s within the boundary band, and the records disagree by up to 10 s; fee upheld, pin far from Tiong Bahru Plaza and the rider says they were there</t>
-        </is>
-      </c>
+          <t>tier: n/a (reclassified to CW-OTHER); reasons: ; profile: organizer_case; reclassified: CW-OTHER</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr"/>
+      <c r="F128" s="7" t="inlineStr"/>
+      <c r="G128" s="7" t="inlineStr"/>
       <c r="H128" s="7" t="inlineStr"/>
       <c r="I128" s="7" t="inlineStr">
         <is>
@@ -26896,32 +26888,40 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="42.5" customHeight="1">
+    <row r="129" ht="191" customHeight="1">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>V118</t>
+          <t>V117</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>the driver canceled and the record gives no reason: ask for the trip record (CLS-06)</t>
+          <t>the reason written RIDER_NO_SHOW is still a driver's no-show cancellation: as DISP-002</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>outcome: REQUEST_INFO; reasons: GEN-R-NEED-INFO; tier: HUMAN</t>
+          <t>outcome: UPHOLD; row: R8; tier: APPROVE</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>outcome: REQUEST_INFO; tier: HUMAN; reasons: GEN-R-NEED-INFO; profile: organizer_case</t>
-        </is>
-      </c>
-      <c r="E129" s="7" t="inlineStr"/>
-      <c r="F129" s="7" t="inlineStr"/>
+          <t>outcome: UPHOLD; row: R8; tier: APPROVE; reasons: CW-R-NOSHOW-VALID; CW-R-PIN-AMBIGUOUS; profile: organizer_case; C: 0.689</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>BOOKING_TYPE_INFERRED; BOUNDARY_MARGIN; MARGIN_WITHIN_SPREAD; NO_RIDER_EVIDENCE; PIN_VENUE_MISMATCH; FRAUD_SIGNAL; GENERIC_ASSUMPTION_USED</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>CW-F04B</t>
+        </is>
+      </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>who canceled is not settled by the trip record, so no fee ruling is made until it is (CLS-06)</t>
+          <t>decisive: CW-F04B (outcome changes when PING_MAX_GAP_S moves within [60, 420]); fraud signal on RIDER (3 of 4 past disputes rejected; platform flag: flagged_for_frequent_late_cancellations) (symmetric trigger; the detail is for the reviewer, not for the parties); fee upheld, and FairRyde's own GPS logic would decide it with PING_MAX_GAP_S at an end of its plausible range (CW-F04B, D29); margin +0 s within the boundary band, and the records disagree by up to 10 s; fee upheld, pin far from Tiong Bahru Plaza and the rider says they were there</t>
         </is>
       </c>
       <c r="H129" s="7" t="inlineStr"/>
@@ -26931,23 +26931,43 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="n"/>
-      <c r="B130" s="2" t="n"/>
-      <c r="C130" s="2" t="n"/>
-      <c r="D130" s="2" t="n"/>
-      <c r="E130" s="2" t="n"/>
-      <c r="F130" s="2" t="n"/>
-      <c r="G130" s="2" t="n"/>
-      <c r="H130" s="2" t="n"/>
-      <c r="I130" s="2" t="n"/>
-    </row>
-    <row r="131" ht="29" customHeight="1">
-      <c r="A131" s="10" t="inlineStr">
-        <is>
-          <t>覆盖：决策表行 R1, R2, R3, R4, R5, R6, R7, R8, R9, R10, R11；自治等级 APPROVE, AUTO, HUMAN, n/a (reclassified to CW-OTHER), n/a (reclassified to CW-RIDERCANCEL)；另有改判（MAT-04 超期、META-02 生效日期、CW-R00 RydeTAXI）和重新分类（V10）。</t>
-        </is>
-      </c>
+    <row r="130" ht="42.5" customHeight="1">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>V118</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>the driver canceled and the record gives no reason: ask for the trip record (CLS-06)</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>outcome: REQUEST_INFO; reasons: GEN-R-NEED-INFO; tier: HUMAN</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>outcome: REQUEST_INFO; tier: HUMAN; reasons: GEN-R-NEED-INFO; profile: organizer_case</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr"/>
+      <c r="F130" s="7" t="inlineStr"/>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>who canceled is not settled by the trip record, so no fee ruling is made until it is (CLS-06)</t>
+        </is>
+      </c>
+      <c r="H130" s="7" t="inlineStr"/>
+      <c r="I130" s="7" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n"/>
       <c r="B131" s="2" t="n"/>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n"/>
@@ -26957,9 +26977,24 @@
       <c r="H131" s="2" t="n"/>
       <c r="I131" s="2" t="n"/>
     </row>
+    <row r="132" ht="29" customHeight="1">
+      <c r="A132" s="10" t="inlineStr">
+        <is>
+          <t>覆盖：决策表行 R1, R2, R3, R4, R5, R6, R7, R8, R9, R10, R11；自治等级 APPROVE, AUTO, HUMAN, n/a (reclassified to CW-OTHER), n/a (reclassified to CW-RIDERCANCEL)；另有改判（MAT-04 超期、META-02 生效日期、CW-R00 RydeTAXI）和重新分类（V10）。</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="n"/>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="2" t="n"/>
+      <c r="E132" s="2" t="n"/>
+      <c r="F132" s="2" t="n"/>
+      <c r="G132" s="2" t="n"/>
+      <c r="H132" s="2" t="n"/>
+      <c r="I132" s="2" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A131:H131"/>
+    <mergeCell ref="A132:H132"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -30850,7 +30885,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>done; implemented in A3 (2026-10-14): CW-F04 keeps Ryde's condition (B) and the new rule CW-F04B holds FairRyde's GPS presence logic (D) with its finding F-GPS-LOGIC, true when the logic and not the pings alone makes the driver count as arrived and present (a ping set aside that could change the presence or the arrival, an outside ping in the window not counted as leaving, a later GPS confirmation, SPARSE or GPS_AMBIGUOUS). No-show fees: DT-CW-NOSHOW input gps_logic_decides; R8 (B) needs it false, the new row R11 (D) is the same uphold when it is true, so the row is decisive and the fee needs approval; the engine also lists the trigger. The ping-gap and radius part: a CW-F04B parameter that would make F-GPS-LOGIC true at an end of its plausible range moves a no-show uphold onto R9 or R11, which decisive_definition clause 2 counts as decisive; for waiting fees (no decision table, D31) AUTH-02 trigger 12 and CW-F04B's text state both parts (check round 1 found the parameter part missing for waiting fees, SG-1 and ADV-1), pointed to from PB-CW-WAITING step 5. The decisive parameter is reported against CW-F04B, or CW-R06 when only the arrival finding moves. The set-aside pings that count are those that could change the presence (in the window) or the arrival (one that would otherwise have been CW-R06's moment ping; with the platform check, only one at or after the indication), check rounds 1 and 2. Check round 2 also made GPS_AMBIGUOUS cover both window edges (ADV2-1, CRITICAL): a driver last seen at the pin more than TS_TOLERANCE_S before the window end and next seen away before the cancellation, and a window that starts after the arrival while the driver was last seen away. Tests: V94 to V103 and ten re-rated variants, an A3 rule-card check, and a fuzz invariant (no automatic uphold with F-GPS-LOGIC true, an outside ping in the window, or a first ping away after the window end that follows a last inside ping more than TS_TOLERANCE_S before the window end). Tier report: validation/build_checks/A3/01b_tier_report.md (DISP-002 and E01 to E04 unchanged). Cost, for Jasper (check round 1, ADV-2): the radius part makes a clean uphold with ordinary GPS jitter (a ping between 10 and 50 m from the pin) go to approval, because at the radius's 10 m low end that ping would be set aside; see D39 (g).</t>
+          <t>done; implemented in A3 (2026-10-14): CW-F04 keeps Ryde's condition (B) and the new rule CW-F04B holds FairRyde's GPS presence logic (D) with its finding F-GPS-LOGIC, true when the logic and not the pings alone makes the driver count as arrived and present (a ping set aside that could change the presence or the arrival, an outside ping in the window not counted as leaving, a later GPS confirmation, SPARSE or GPS_AMBIGUOUS). No-show fees: DT-CW-NOSHOW input gps_logic_decides; R8 (B) needs it false, the new row R11 (D) is the same uphold when it is true, so the row is decisive and the fee needs approval; the engine also lists the trigger. The ping-gap and radius part: a CW-F04B parameter that would make F-GPS-LOGIC true at an end of its plausible range moves a no-show uphold onto R9 or R11, which decisive_definition clause 2 counts as decisive; for waiting fees (no decision table, D31) AUTH-02 trigger 12 and CW-F04B's text state both parts (check round 1 found the parameter part missing for waiting fees, SG-1 and ADV-1), pointed to from PB-CW-WAITING step 5. The decisive parameter is reported against CW-F04B, or CW-R06 when only the arrival finding moves. The set-aside pings that count are those that could change the presence (in the window) or the arrival (one that would otherwise have been CW-R06's moment ping; with the platform check, only one at or after the indication), check rounds 1 and 2. Check round 2 also made GPS_AMBIGUOUS cover both window edges (ADV2-1, CRITICAL): a driver last seen at the pin more than TS_TOLERANCE_S before the window end and next seen away before the cancellation, and a window that starts after the arrival while the driver was last seen away. Tests: V94 to V103 and ten re-rated variants, an A3 rule-card check, and a fuzz invariant (no automatic uphold with F-GPS-LOGIC true, an outside ping in the window, or a first ping away after the window end that follows a last inside ping more than TS_TOLERANCE_S before the window end). Tier report: validation/build_checks/A3/01b_tier_report.md (DISP-002 and E01 to E04 unchanged). Cost, for Jasper (check round 1, ADV-2): the radius part makes a clean uphold with ordinary GPS jitter (a ping between 10 and 50 m from the pin) go to approval, because at the radius's 10 m low end that ping would be set aside; see D39 (g). Jasper, 2026-10-14: the radius's plausible range starts at 20 m, above ordinary phone GPS error (reasons in reference_data.yaml); a ping between 20 and 50 m from the pin still sends the uphold to approval. In the jitter simulation (600 clean upholds, seed 5) automatic upholds go from 29 back to 204 (A2: 235); V99 and V99B pin both sides.</t>
         </is>
       </c>
     </row>
@@ -31012,7 +31047,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>done in A2 (Jasper's step prompt, 2026-10-11). Corrections after check round 1: the first version defaulted every other service to share 1.0 and capped the refund at the ERP charged; both were wrong (RydePOOL pages say 50%, and a rider charged less than ERP(actual) was refunded money owed on the recommended route). Still open: (1) organizer or Ryde, question O15: RydePOOL (2026 driver pages: each rider pays 50% of the total toll; 2023 driver pages: RydePOOL, RydeHIRE and RydeSEND fares include ERP), RydeHIRE, Ryde X GO and Ryde+, and on a carpool trip whether the driver keys the total ERP or the passenger's half and how the passenger half divides among several passengers (a backlog item in scope.yaml); (2) Jasper to confirm that FC-R01 opens the FC-TOLL claim without the rider naming the ERP (FairRyde design, D), and that it does so only for a fixed fare charged as quoted: on a RECALCULATED fare or a charged fare different from the quote nothing opens the claim unless the rider names the ERP; (3) the same PDVL-only scope applies to the LTA citations in FC-F03 and FC-R03 (not changed in A2), and FC-R08 does not check which kind of driver served the trip (a taxi driver on RydeX, a carpool driver without a PDVL); (4) FC-F03 stays C because of its DiDi element, but Ryde states the GPS permission for fixed fares, so using it for ERP claims extends it: A3's census rates it (done: D in A3, see D39); (5) FC-R07: the refund of the difference is FairRyde's remedy (as in FC-R10, D); by the credibility principle the rule would be D, left at A in A2 for Jasper to decide (recommended: D in A3; done: D in A3 on Jasper's decision of 2026-10-14); (6) the engine takes the gantry log's rate over the LTA table when both exist (E11: the table lists S$6.00 for that gantry in a later window), and a disagreement is not flagged; it also reads the HH:MM of a table lookup without the timestamp's offset and counts two identical rows of the gantry log as two passes (check round 2, not fixed); (7) RydePOOL and RydeHIRE: the 2026 and 2023 driver pages contradict each other (and the 2024 rider page says ERP is excluded for every service but RydeSEND), so this could be a META-04 known conflict (SOURCE_CONFLICT, GEN-R-SOURCE-CONFLICT) instead of GEN-R07; A2 uses GEN-R07, Jasper to choose; (8) the 50% of a carpool trip holds for one passenger, the record has no rider count, and several passengers are a scope.yaml backlog item (check round 2); (9) carpool status: whether the case data can say it at all, and whether Ryde means a trip by a carpool driver (RydeFLASH is offered to them) or a shared ride (organizer or Ryde, O15). Check round 2 (A2) fixed: the carpool flag overriding the no-share list, the RydeFLASH default, route_review without the recommended route, numeric and boolean parsing, the refund-sum sentence. Jasper's decisions of 2026-10-14 on these points: (2) FC-R01 stays as it is (it opens the FC-TOLL claim without the rider naming the ERP, and only for a fixed fare charged as quoted); (5) FC-R07 goes to credibility D in A3; (7) the services with no ERP share in ERP_RIDER_SHARE (RydePOOL, RydeHIRE, Ryde X GO, Ryde+, RydeSEND plus carpool) stay with a person under GEN-R07, not META-04; (8) the carpool half (0.5) stays for one passenger only, and an is_carpool that is not recorded stays as implemented in A2: it goes to a person for confirmation where it matters (RydeFLASH, which Ryde offers to carpool drivers: RECORDS_MISSING, tier APPROVE); for the other services it reads as not carpool (A3 check round 1, CONS-7: to confirm with Jasper whether the decision meant RydeFLASH only, as implemented, or every service). Items (1), (3), (6) and (9) stay open, and (8) waits for Jasper's answer on its scope.</t>
+          <t>done in A2 (Jasper's step prompt, 2026-10-11). Corrections after check round 1: the first version defaulted every other service to share 1.0 and capped the refund at the ERP charged; both were wrong (RydePOOL pages say 50%, and a rider charged less than ERP(actual) was refunded money owed on the recommended route). Still open: (1) organizer or Ryde, question O15: RydePOOL (2026 driver pages: each rider pays 50% of the total toll; 2023 driver pages: RydePOOL, RydeHIRE and RydeSEND fares include ERP), RydeHIRE, Ryde X GO and Ryde+, and on a carpool trip whether the driver keys the total ERP or the passenger's half and how the passenger half divides among several passengers (a backlog item in scope.yaml); (2) Jasper to confirm that FC-R01 opens the FC-TOLL claim without the rider naming the ERP (FairRyde design, D), and that it does so only for a fixed fare charged as quoted: on a RECALCULATED fare or a charged fare different from the quote nothing opens the claim unless the rider names the ERP; (3) the same PDVL-only scope applies to the LTA citations in FC-F03 and FC-R03 (not changed in A2), and FC-R08 does not check which kind of driver served the trip (a taxi driver on RydeX, a carpool driver without a PDVL); (4) FC-F03 stays C because of its DiDi element, but Ryde states the GPS permission for fixed fares, so using it for ERP claims extends it: A3's census rates it (done: D in A3, see D39); (5) FC-R07: the refund of the difference is FairRyde's remedy (as in FC-R10, D); by the credibility principle the rule would be D, left at A in A2 for Jasper to decide (recommended: D in A3; done: D in A3 on Jasper's decision of 2026-10-14); (6) the engine takes the gantry log's rate over the LTA table when both exist (E11: the table lists S$6.00 for that gantry in a later window), and a disagreement is not flagged; it also reads the HH:MM of a table lookup without the timestamp's offset and counts two identical rows of the gantry log as two passes (check round 2, not fixed); (7) RydePOOL and RydeHIRE: the 2026 and 2023 driver pages contradict each other (and the 2024 rider page says ERP is excluded for every service but RydeSEND), so this could be a META-04 known conflict (SOURCE_CONFLICT, GEN-R-SOURCE-CONFLICT) instead of GEN-R07; A2 uses GEN-R07, Jasper to choose; (8) the 50% of a carpool trip holds for one passenger, the record has no rider count, and several passengers are a scope.yaml backlog item (check round 2); (9) carpool status: whether the case data can say it at all, and whether Ryde means a trip by a carpool driver (RydeFLASH is offered to them) or a shared ride (organizer or Ryde, O15). Check round 2 (A2) fixed: the carpool flag overriding the no-share list, the RydeFLASH default, route_review without the recommended route, numeric and boolean parsing, the refund-sum sentence. Jasper's decisions of 2026-10-14 on these points: (2) FC-R01 stays as it is (it opens the FC-TOLL claim without the rider naming the ERP, and only for a fixed fare charged as quoted); (5) FC-R07 goes to credibility D in A3; (7) the services with no ERP share in ERP_RIDER_SHARE (RydePOOL, RydeHIRE, Ryde X GO, Ryde+, RydeSEND plus carpool) stay with a person under GEN-R07, not META-04; (8) the carpool half (0.5) stays for one passenger only, and an is_carpool that is not recorded stays as implemented in A2: it goes to a person for confirmation where it matters (RydeFLASH, which Ryde offers to carpool drivers: RECORDS_MISSING, tier APPROVE); for the other services it reads as not carpool (A3 check round 1, CONS-7: to confirm with Jasper whether the decision meant RydeFLASH only, as implemented, or every service). Items (1), (3), (6) and (9) stay open. (8) decided by Jasper on 2026-10-14: an unrecorded is_carpool goes to a person only for RydeFLASH, as implemented; for the other services it reads as not carpool.</t>
         </is>
       </c>
     </row>
@@ -31120,7 +31155,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>done in A3. Judgments for Jasper, not changed: (a) CW-R06 stays B: its FairRyde parts (the outlier step, the later confirmation, CONTESTED, UNKNOWN) are rated D in the rules they belong to (CW-F04B, CW-F03B, GEN-R02, GEN-R01); every row whose ruling rests on them is D (R2, R3, R9, R11), except a short-wait waiver (R6, A) that rests on a later confirmation, which CW-F03B's start test sends to approval when another reading changes it; reading Ryde's GPS condition at the moment of the arrival through the last remaining ping from PING_MAX_GAP_S before to TS_TOLERANCE_S after it is counted as Ryde's condition, with its look-back, tolerance and radius as D parameters tested by the sensitivity test; (b) FC-R01 stays B: recording the deviation as conduct information and opening the FC-TOLL claim are FairRyde's (D) but set no amount and add no condition to the no-refund finding; (c) AUTH-03 stays B: a human deciding (not only approving) safety matters is stricter than the IMDA guidance and only sends more cases to people; (d) R1 and R4 stay B: setting a ping aside only removes evidence that the driver was away, so a FALSE arrival or LEFT found with the logic also holds on the pings alone, except a data error (gate G1, approval); (e) CW-R08 would be C again with a local source for its 'not moving' ground (Grab's cancellation page) and, since A4, for its advance-booking ETA; (f) FX9 leftovers seen in the census, done in A4: CW-F02B cites the 2024 driver page RYDE-20244064619161, and CW-R08 defines the assignment ETA of an advance booking (see D40). Check round 1 (A3) added: (a') the reviewers note that 'delegated' is the builder's category, not FX4's wording; if Jasper reads FX4 literally, CW-R06 is D, R1 and R8 become D, and every no-show uphold and every R1 waiver goes to approval; the alternative is to split CW-R06 as CW-F04 was; (b') and (c') are the same kind of judgment (a FairRyde step in the conclusion of FC-R01; a stricter-than-source reading in AUTH-03); (g) the radius part of D29 (ADV-2): with pings 3 m from the pin and one at 15 m, V99 now goes to approval (it was automatic in A2); a reviewer's simulation of 600 clean upholds on the round 1 draft (parked 0 to 25 m from the pin, normal jitter) found automatic upholds falling from 38% to 5% (198 of the 201 moved cases through ARRIVAL_GEOFENCE_M's 10 m low end, 3 through TS_TOLERANCE_S); the builder's run (validation/build_checks/A3/jitter_sim.py) gives 235 to 29 of 600, every moved case through the radius; options: keep it (D29 as written), exempt the radius from the row-move part of clause 2, or raise the radius's low end above the platform's 10 m check; (h) the toll engine does not mark FC-R07's refund (now D) as a generic assumption: META-05 needs a decisive rule and decisive_definition makes a D outcome rule decisive only through a decision-table row; every FC-R07 refund already needs approval because of the fraud signal; (i) pre-existing engine defect fixed in A3 (ADV-3): pings were sorted by their timestamp text, so pings written with another UTC offset were read out of order (a departure became an outlier); they are now sorted by instant (V98), and read on the trip record's clock. Check round 2 (A3) added: (j) pre-existing, not fixed: a GPS timestamp without a UTC offset makes the engine stop with an error (no ruling, no tier), so such a case reaches no automatic ruling but also no routing; normalizing it needs a data-quality rule (DQ-03 or DQ-04); (k) frozen area (D34), not fixed: the reader's answers_question orders the driver's messages by their timestamp text, the defect fixed for GPS pings in (i); (l) the fuzz generator makes no advance bookings; V101 and V103 pin the advance-booking edges.</t>
+          <t>done in A3. Judgments for Jasper, not changed: (a) CW-R06 stays B: its FairRyde parts (the outlier step, the later confirmation, CONTESTED, UNKNOWN) are rated D in the rules they belong to (CW-F04B, CW-F03B, GEN-R02, GEN-R01); every row whose ruling rests on them is D (R2, R3, R9, R11), except a short-wait waiver (R6, A) that rests on a later confirmation, which CW-F03B's start test sends to approval when another reading changes it; reading Ryde's GPS condition at the moment of the arrival through the last remaining ping from PING_MAX_GAP_S before to TS_TOLERANCE_S after it is counted as Ryde's condition, with its look-back, tolerance and radius as D parameters tested by the sensitivity test; (b) FC-R01 stays B: recording the deviation as conduct information and opening the FC-TOLL claim are FairRyde's (D) but set no amount and add no condition to the no-refund finding; (c) AUTH-03 stays B: a human deciding (not only approving) safety matters is stricter than the IMDA guidance and only sends more cases to people; (d) R1 and R4 stay B: setting a ping aside only removes evidence that the driver was away, so a FALSE arrival or LEFT found with the logic also holds on the pings alone, except a data error (gate G1, approval); (e) CW-R08 would be C again with a local source for its 'not moving' ground (Grab's cancellation page) and, since A4, for its advance-booking ETA; (f) FX9 leftovers seen in the census, done in A4: CW-F02B cites the 2024 driver page RYDE-20244064619161, and CW-R08 defines the assignment ETA of an advance booking (see D40). Check round 1 (A3) added: (a') the reviewers note that 'delegated' is the builder's category, not FX4's wording; if Jasper reads FX4 literally, CW-R06 is D, R1 and R8 become D, and every no-show uphold and every R1 waiver goes to approval; the alternative is to split CW-R06 as CW-F04 was; (b') and (c') are the same kind of judgment (a FairRyde step in the conclusion of FC-R01; a stricter-than-source reading in AUTH-03); (g) the radius part of D29 (ADV-2): with pings 3 m from the pin and one at 15 m, V99 now goes to approval (it was automatic in A2); a reviewer's simulation of 600 clean upholds on the round 1 draft (parked 0 to 25 m from the pin, normal jitter) found automatic upholds falling from 38% to 5% (198 of the 201 moved cases through ARRIVAL_GEOFENCE_M's 10 m low end, 3 through TS_TOLERANCE_S); the builder's run (validation/build_checks/A3/jitter_sim.py) gives 235 to 29 of 600, every moved case through the radius; options: keep it (D29 as written), exempt the radius from the row-move part of clause 2, or raise the radius's low end above the platform's 10 m check; (h) the toll engine does not mark FC-R07's refund (now D) as a generic assumption: META-05 needs a decisive rule and decisive_definition makes a D outcome rule decisive only through a decision-table row; every FC-R07 refund already needs approval because of the fraud signal; (i) pre-existing engine defect fixed in A3 (ADV-3): pings were sorted by their timestamp text, so pings written with another UTC offset were read out of order (a departure became an outlier); they are now sorted by instant (V98), and read on the trip record's clock. Check round 2 (A3) added: (j) pre-existing, not fixed: a GPS timestamp without a UTC offset makes the engine stop with an error (no ruling, no tier), so such a case reaches no automatic ruling but also no routing; normalizing it needs a data-quality rule (DQ-03 or DQ-04); (k) frozen area (D34), not fixed: the reader's answers_question orders the driver's messages by their timestamp text, the defect fixed for GPS pings in (i); (l) the fuzz generator makes no advance bookings; V101 and V103 pin the advance-booking edges. Jasper's decisions of 2026-10-14: (a), (b) and (c) CW-R06, FC-R01 and AUTH-03 stay B as they are; (g) the radius's low end is raised to 20 m, above ordinary phone GPS error (D29; ARRIVAL_GEOFENCE_M in reference_data.yaml, credibility D); the other points stay as recorded.</t>
         </is>
       </c>
     </row>
@@ -31147,7 +31182,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>done in A4. For Jasper: (a) the reference engine's safety check is still a list (SAFETY_PATTERNS, whole-word patterns since check round 1, erring toward safety); it misses paraphrases that use none of its patterns (a reviewer found 22 of 22 such texts missed), so it is a test stand-in, not the classifier; the definition is for the LLM classifier, and validation round 2's taxonomy texts test it; (b) FC-FAREMISMATCH and FC-DRIVERCHARGE are BACKLOG (a person decides); a driver who made up a charge may also deserve a fraud signal (FRD-01 does not cover it yet); (c) discrimination now makes a claim SE-CONDUCT and primary even when the complaint is mainly about a fee (C05's discriminatory refusal is now a safety claim, not CW-DRIVERNOSHOW); (d) the case data has no field for several drop-offs in the organizer's sample (trip_data.stops is a data gap). Check round 1 (A4) added: (e) CLS-01 now counts abuse or harassment of any kind (insults, slurs, personal questions, comments on appearance, personal contact after the trip) as safety content, following Ryde's Code of Conduct item 5, and keeps only an unfriendly manner, a raised voice or a curt reply as feedback; where that line lies is FairRyde's design and Jasper's call; (f) CLS-01 no longer names a rider under the influence (Ryde's text is about the driver), and being stranded counts only when the driver made the passenger leave or left them behind, so a cleaning claim about a drunk rider or a cancellation complaint saying 'stranded' is not safety content by those examples alone; (g) the engine records no secondary EX-FEEDBACK claim for a rudeness complaint (V107); the claim splitting of CLS-02 is for the LLM classifier; (h) FC-R12 for a changed itinerary now applies only when the recommended route can change the amount, so a RydeSEND claim or one with no ERP passed or charged keeps its automatic ruling; (i) a reclassified case with safety content now goes to a person (gate G4), as CLS-01 requires; (j) safety_termination does not name the party, so CLS-06 takes the party from the other records. Check round 2 (A4) added: (k) a CW-R08 waiver can be automatic: CW-R08 is D, but decisive_definition makes a D outcome rule decisive only through a decision-table row and CW-RIDERCANCEL has no table (the same gap as D39 (h) for FC-R07); A4 narrowed the 'not moving' ground for advance bookings (an early driver waiting nearby is not a ground), and whether every CW-R08 waiver should need approval is Jasper's call; (l) the reference engines read the trip record's wording with patterns (canceling_party in engine_noshow.py, itinerary_change in engine_toll.py); a record they cannot read counts as disagreeing or as a possible change, so it goes to a person, never to an automatic ruling.</t>
+          <t>done in A4. For Jasper: (a) the reference engine's safety check is still a list (SAFETY_PATTERNS, whole-word patterns since check round 1, erring toward safety); it misses paraphrases that use none of its patterns (a reviewer found 22 of 22 such texts missed), so it is a test stand-in, not the classifier; the definition is for the LLM classifier, and validation round 2's taxonomy texts test it; (b) FC-FAREMISMATCH and FC-DRIVERCHARGE are BACKLOG (a person decides); a driver who made up a charge may also deserve a fraud signal (FRD-01 does not cover it yet); (c) discrimination now makes a claim SE-CONDUCT and primary even when the complaint is mainly about a fee (C05's discriminatory refusal is now a safety claim, not CW-DRIVERNOSHOW); (d) the case data has no field for several drop-offs in the organizer's sample (trip_data.stops is a data gap). Check round 1 (A4) added: (e) CLS-01 now counts abuse or harassment of any kind (insults, slurs, personal questions, comments on appearance, personal contact after the trip) as safety content, following Ryde's Code of Conduct item 5, and keeps only an unfriendly manner, a raised voice or a curt reply as feedback; where that line lies is FairRyde's design and Jasper's call; (f) CLS-01 no longer names a rider under the influence (Ryde's text is about the driver), and being stranded counts only when the driver made the passenger leave or left them behind, so a cleaning claim about a drunk rider or a cancellation complaint saying 'stranded' is not safety content by those examples alone; (g) the engine records no secondary EX-FEEDBACK claim for a rudeness complaint (V107); the claim splitting of CLS-02 is for the LLM classifier; (h) FC-R12 for a changed itinerary now applies only when the recommended route can change the amount, so a RydeSEND claim or one with no ERP passed or charged keeps its automatic ruling; (i) a reclassified case with safety content now goes to a person (gate G4), as CLS-01 requires; (j) safety_termination does not name the party, so CLS-06 takes the party from the other records. Check round 2 (A4) added: (k) a CW-R08 waiver can be automatic: CW-R08 is D, but decisive_definition makes a D outcome rule decisive only through a decision-table row and CW-RIDERCANCEL has no table (the same gap as D39 (h) for FC-R07); A4 narrowed the 'not moving' ground for advance bookings (an early driver waiting nearby is not a ground), and whether every CW-R08 waiver should need approval is Jasper's call; (l) the reference engines read the trip record's wording with patterns (canceling_party in engine_noshow.py, itinerary_change in engine_toll.py); a record they cannot read counts as disagreeing or as a possible change, so it goes to a person, never to an automatic ruling. Jasper's decisions of 2026-10-14: (a) the engine's safety pattern list and (d) the missing field for several drop-offs (trip_data.stops) are known limitations of v0.2; (e) the line between rudeness and abuse stays as A4 drew it; (k) every CW-R08 waiver needs approval, in line with D29 (AUTH-02 trigger 13, CW-R08, PB-CW-RIDERCANCEL step 5).</t>
         </is>
       </c>
     </row>

--- a/kb/out/FairRyde_KB_v0.2.xlsx
+++ b/kb/out/FairRyde_KB_v0.2.xlsx
@@ -610,7 +610,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>FairRyde_KB_v0.2.xlsx（本文件）：知识库，每次运行 build_kb.py 重新生成，不放任何标注。FairRyde_Annotation_v0.2.xlsx：标注工作簿，脚本只建一次；只要有人填过人工列，或文件正在 Excel 或 LibreOffice 里打开，脚本就不会覆盖它（ONT.11.3）。本次运行：FairRyde_Annotation_v0.2.xlsx 已生成（没有人工填写过），旧文件备份到 backup/FairRyde_Annotation_v0.2.20261014T120616.xlsx</t>
+          <t>FairRyde_KB_v0.2.xlsx（本文件）：知识库，每次运行 build_kb.py 重新生成，不放任何标注。FairRyde_Annotation_v0.2.xlsx：标注工作簿，脚本只建一次；只要有人填过人工列，或文件正在 Excel 或 LibreOffice 里打开，脚本就不会覆盖它（ONT.11.3）。本次运行：FairRyde_Annotation_v0.2.xlsx 已生成（没有人工填写过），旧文件备份到 backup/FairRyde_Annotation_v0.2.20261014T125627.xlsx</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>规则 90 条；逐字引文 148 条与原文一致，不符 0 条；DISP-002 的 59 个字段全部映射到本体；决策表 192 种输入组合每种恰好命中一行；引擎自测 126/126 通过；生成文件的隐私泄漏扫描命中 0 处；错误 0 个，警告 0 个。</t>
+          <t>规则 90 条；逐字引文 149 条与原文一致，不符 0 条；DISP-002 的 59 个字段全部映射到本体；决策表 192 种输入组合每种恰好命中一行；引擎自测 128/128 通过；生成文件的隐私泄漏扫描命中 0 处；错误 0 个，警告 0 个。</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>126 个单因素变体，检验规则卡与参考引擎一致（不是标准答案）</t>
+          <t>128 个单因素变体，检验规则卡与参考引擎一致（不是标准答案）</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>案件里任何自由文本（描述、聊天、补充证据）含有安全相关内容时，单独建 SE 主张，定严重度 S0 或 S1，转人工，不管工单里还有什么。安全相关内容是任何一方讲述的以下情形：暴力或暴力威胁（攻击或企图攻击、打人、抓伤、凶器、威胁恐吓）；性不当行为（骚扰、不受欢迎的示好或触碰）；对人的任何形式的辱骂或骚扰（侮辱、带歧视的辱骂或冲人骂脏话、过分私人的问题、评论外貌、行程后因私联系乘客）；被违背意愿扣留或带走（绑架、劫持，司机不让乘客下车或要求停车也不停）；被置于危险之中（鲁莽或危险驾驶，司机受酒精或药物影响，不安全的下车，例如被赶下车留在快速公路或路肩上，或在偏僻处、夜里被司机赶下车或丢下）；事故或受伤；因种族、族裔、宗教、国籍、残疾或类似理由受到歧视；或其他犯罪。按意思判断，不按关键词：这些只是例子，不是封闭清单，没用这些词的文字也可能是安全内容（"他停在 PIE 上叫我下车"）。拿不准是不是安全内容时按安全内容处理（S1），让人工看到。只是态度不好（不友善或不耐烦、大声、回话生硬），没有辱骂、威胁、危险或歧视，不是安全内容，属于一般反馈（EX-FEEDBACK）。关于钱的争议（车费、费用、多收、司机自己加的收费）或车辆损坏，本身不是安全内容，即使这种行为可能构成犯罪；伴有暴力、威胁、危险、辱骂或歧视时才是安全内容。有人受伤、被扣留、被攻击、受到伤害威胁或处于紧迫危险时为 S0，其余为 S1。SE 类型按分类定义选（对人的行为为 SE-CONDUCT，另有 SE-DRIVING、SE-ACCIDENT，行程中途被终止为 SE-TERMINATED，司机或车辆与 App 不符为 SE-MISMATCH，车内录像设备为 SE-RECORDING，其余为 SE-OTHER）。</t>
+          <t>案件里任何自由文本（描述、聊天、补充证据）含有安全相关内容时，单独建 SE 主张，定严重度 S0 或 S1，转人工，不管工单里还有什么。安全相关内容是任何一方讲述的以下情形：暴力或暴力威胁（攻击或企图攻击、打人、抓伤、凶器、威胁恐吓）；性不当行为（骚扰、不受欢迎的示好或触碰）；对人的任何形式的辱骂或骚扰（侮辱、带歧视的辱骂或冲人骂脏话、过分私人的问题、评论外貌、行程后因私联系乘客）；被违背意愿扣留或带走（绑架、劫持，司机不让乘客下车或要求停车也不停）；被置于危险之中（鲁莽或危险驾驶，司机受酒精或药物影响，不安全的下车，例如被赶下车留在快速公路或路肩上，或在偏僻处、夜里被司机赶下车或丢下）；事故或受伤；因种族、族裔、宗教、国籍、残疾或类似理由受到歧视；或其他犯罪。按意思判断，不按关键词：这些只是例子，不是封闭清单，没用这些词的文字也可能是安全内容（"他停在 PIE 上叫我下车"）。拿不准是不是安全内容时按安全内容处理（S1），让人工看到。只是态度不好（不友善或不耐烦、大声、回话生硬），没有辱骂、威胁、危险或歧视，不是安全内容，属于一般反馈（EX-FEEDBACK）。关于钱的争议（车费、费用、多收、司机自己加的收费）或车辆损坏，本身不是安全内容，即使这种行为可能构成犯罪；伴有暴力、威胁、危险、辱骂或歧视时才是安全内容。有人受伤、被扣留、被攻击、受到伤害威胁或处于紧迫危险时为 S0，其余为 S1。提到歧视的投诉一律是安全内容，整个案子转人工：AI 只准备案卷（主张、证据、事实认定），对其中任何主张都不给结果、金额或措施建议；争议费用作为次要诉求写进案卷（CLS-02、SE-R01；Jasper，2026-10-14，待办 D40 (c)）。SE 类型按分类定义选（对人的行为为 SE-CONDUCT，另有 SE-DRIVING、SE-ACCIDENT，行程中途被终止为 SE-TERMINATED，司机或车辆与 App 不符为 SE-MISMATCH，车内录像设备为 SE-RECORDING，其余为 SE-OTHER）。</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>If any free text in the case (description, chat, added evidence) contains safety content, create an SE claim, set severity S0 or S1 and route it to a human, whatever else the ticket contains. Safety content is any account, by either party, of: violence or its threat (assault or an attempt, hitting, scratching, a weapon, threats and intimidation); sexual misconduct (harassment, unwanted advances or touching); abuse or harassment of any kind toward a person (insults, slurs or swearing at someone, overly personal questions, comments on someone's appearance, contacting a passenger after the trip for personal reasons); being held or taken against one's will (kidnapping or abduction, a driver who will not let the passenger out or will not stop when asked); being put in danger (reckless or dangerous driving, a driver under the influence of drink or drugs, an unsafe drop-off such as being made to leave the car on an expressway or road shoulder, or being made to leave the car, or left behind by the driver, at an isolated place or at night); an accident or an injury; discrimination because of race, ethnicity, religion, nationality, disability or a similar ground; or any other crime. It is judged by meaning, not by keywords: these are examples, not a closed list, and text that uses none of these words can be safety content ("he stopped on the PIE and told me to get out"). When it is unclear whether text is safety content, it is treated as safety content (S1), so a person sees it. Rudeness alone (an unfriendly or impatient manner, a raised voice, a curt reply) with no abuse, threat, danger or discrimination is not safety content; it is feedback (EX-FEEDBACK). A dispute about money (a fare, a fee, an overcharge, a charge the driver made up) or about damage to the car is not safety content by itself, even where the conduct may be a crime; it becomes safety content when it comes with violence, threats, danger, abuse or discrimination. Severity S0 when someone was hurt, held, assaulted, threatened with harm or put in immediate danger; S1 otherwise. The SE type follows the taxonomy definitions (SE-CONDUCT for behavior toward a person, SE-DRIVING, SE-ACCIDENT, SE-TERMINATED for a ride ended midway, SE-MISMATCH for a driver or car that does not match the app, SE-RECORDING for an in-vehicle recording device, SE-OTHER otherwise).</t>
+          <t>If any free text in the case (description, chat, added evidence) contains safety content, create an SE claim, set severity S0 or S1 and route it to a human, whatever else the ticket contains. Safety content is any account, by either party, of: violence or its threat (assault or an attempt, hitting, scratching, a weapon, threats and intimidation); sexual misconduct (harassment, unwanted advances or touching); abuse or harassment of any kind toward a person (insults, slurs or swearing at someone, overly personal questions, comments on someone's appearance, contacting a passenger after the trip for personal reasons); being held or taken against one's will (kidnapping or abduction, a driver who will not let the passenger out or will not stop when asked); being put in danger (reckless or dangerous driving, a driver under the influence of drink or drugs, an unsafe drop-off such as being made to leave the car on an expressway or road shoulder, or being made to leave the car, or left behind by the driver, at an isolated place or at night); an accident or an injury; discrimination because of race, ethnicity, religion, nationality, disability or a similar ground; or any other crime. It is judged by meaning, not by keywords: these are examples, not a closed list, and text that uses none of these words can be safety content ("he stopped on the PIE and told me to get out"). When it is unclear whether text is safety content, it is treated as safety content (S1), so a person sees it. Rudeness alone (an unfriendly or impatient manner, a raised voice, a curt reply) with no abuse, threat, danger or discrimination is not safety content; it is feedback (EX-FEEDBACK). A dispute about money (a fare, a fee, an overcharge, a charge the driver made up) or about damage to the car is not safety content by itself, even where the conduct may be a crime; it becomes safety content when it comes with violence, threats, danger, abuse or discrimination. Severity S0 when someone was hurt, held, assaulted, threatened with harm or put in immediate danger; S1 otherwise. A complaint that mentions discrimination is always safety content, and the whole case goes to a person: FairRyde prepares the case file (the claims, the evidence and the findings) and proposes no outcome, amount or measure for any claim in it, and a contested fee is recorded in the file as a secondary claim (CLS-02, SE-R01; Jasper, 2026-10-14, open item D40 (c)). The SE type follows the taxonomy definitions (SE-CONDUCT for behavior toward a person, SE-DRIVING, SE-ACCIDENT, SE-TERMINATED for a ride ended midway, SE-MISMATCH for a driver or car that does not match the app, SE-RECORDING for an in-vehicle recording device, SE-OTHER otherwise).</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="P13" s="5" t="inlineStr"/>
     </row>
-    <row r="14" ht="177.5" customHeight="1">
+    <row r="14" ht="218" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>CLS-02</t>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>每个争议款项或问题一个主张。安全主张（任何 SE 类型，不论是 CLS-01 建的还是分类时选的）永远是主项；没有安全主张时，争议金额最大的主张为主项；再没有时，以最先提出的问题为主项。其他主张为次项。自由文本与组织方争议代码矛盾时，代码仍为主项，文字所述问题列为次项，并标记复核（安全主张仍优先于代码）。</t>
+          <t>每个争议款项或问题一个主张。安全主张（任何 SE 类型，不论是 CLS-01 建的还是分类时选的）永远是主项；没有安全主张时，争议金额最大的主张为主项；再没有时，以最先提出的问题为主项。其他主张为次项。自由文本与组织方争议代码矛盾时，代码仍为主项，文字所述问题列为次项，并标记复核（安全主张仍优先于代码）。提到歧视的案子里，争议费用是写进案卷的次要诉求，不给任何结果建议（CLS-01）。</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>One claim per contested charge or issue. A safety claim (any SE type, whether CLS-01 created it or the classification chose an SE type for it) is always the primary claim; otherwise the primary claim is the one contesting the largest charge; otherwise the first stated issue. Other claims are secondary. If the free text contradicts the organizer's dispute code, the code stays primary, the text's issue becomes a secondary claim, and the case is flagged for review; a safety claim still comes first.</t>
+          <t>One claim per contested charge or issue. A safety claim (any SE type, whether CLS-01 created it or the classification chose an SE type for it) is always the primary claim; otherwise the primary claim is the one contesting the largest charge; otherwise the first stated issue. Other claims are secondary. If the free text contradicts the organizer's dispute code, the code stays primary, the text's issue becomes a secondary claim, and the case is flagged for review; a safety claim still comes first. In a case that mentions discrimination, a contested fee is a secondary claim recorded in the case file, with no proposed outcome (CLS-01).</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="P74" s="5" t="inlineStr"/>
     </row>
-    <row r="75" ht="96.5" customHeight="1">
+    <row r="75" ht="150.5" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
           <t>SE-R01</t>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>安全类主张由 AI 分类、保全证据、写中立摘要，可建议可逆的临时措施（如不再匹配二人），由人裁决。</t>
+          <t>安全类主张由 AI 分类、保全证据、写中立摘要，可建议可逆的临时措施（如不再匹配二人），由人裁决。投诉提到歧视时，AI 只准备案卷，对案子里任何主张都不给任何建议，临时措施也不建议（CLS-01；Jasper，2026-10-14，待办 D40 (c)）。</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>For any SE claim, FairRyde classifies, preserves and hashes the evidence, writes a neutral summary and may recommend reversible interim measures (for example not matching the two parties again); a human decides.</t>
+          <t>For any SE claim, FairRyde classifies, preserves and hashes the evidence, writes a neutral summary and may recommend reversible interim measures (for example not matching the two parties again); a human decides. When the complaint mentions discrimination, FairRyde only prepares the case file and makes no recommendation of any kind, not even an interim measure, on any claim in the case (CLS-01; Jasper, 2026-10-14, open item D40 (c)).</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="P85" s="5" t="inlineStr"/>
     </row>
-    <row r="86" ht="191" customHeight="1">
+    <row r="86" ht="326" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
         <is>
           <t>FRD-01</t>
@@ -7042,12 +7042,12 @@
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>无 GPS 在点却标到达（CW-R06 为 FALSE；或没有平台到达校验时，到达标记 TS_TOLERANCE_S 之后、GPS 首次确认之前有剩下的点在半径外；容差以内的点不算证据，CONTESTED 交给人工、不打信号）、接单后不动且不联系、同一地点反复 no-show，对司机打欺诈信号；后果由人决定。</t>
+          <t>无 GPS 在点却标到达（CW-R06 为 FALSE；或没有平台到达校验时，到达标记 TS_TOLERANCE_S 之后、GPS 首次确认之前有剩下的点在半径外；容差以内的点不算证据，CONTESTED 交给人工、不打信号）、接单后不动且不联系、同一地点反复 no-show、或司机向乘客收取 app 车费不包含的费用（FC-DRIVERCHARGE：司机自己加的费用、要求额外付款、要求在 app 外转账；Jasper，2026-10-14，待办 D40 (b)），对司机打欺诈信号。和 FRD-02 对乘客信号的规定一样，欺诈信号不改变判决结果（GEN-R03），只给审核人看、不给双方看，并需人工批准（AUTH-02 第 2 项）。后果由人决定。</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Raise FRAUD_SIGNAL against the driver if: arrival was indicated without GPS presence (CW-R06 FALSE, or, with no platform arrival check, a remaining GPS ping outside the pick-up area more than TS_TOLERANCE_S after the arrival indication and before GPS first confirmed the driver there; pings within the tolerance are not evidence either way, and a CONTESTED arrival goes to a person without a signal); the driver stayed stationary and uncontactable after accepting; or repeated no-show cancellations occur at the same spot. A human decides any consequence.</t>
+          <t>Raise FRAUD_SIGNAL against the driver if: arrival was indicated without GPS presence (CW-R06 FALSE, or, with no platform arrival check, a remaining GPS ping outside the pick-up area more than TS_TOLERANCE_S after the arrival indication and before GPS first confirmed the driver there; pings within the tolerance are not evidence either way, and a CONTESTED arrival goes to a person without a signal); the driver stayed stationary and uncontactable after accepting; repeated no-show cancellations occur at the same spot; or the driver charged the rider something the app's fare does not include (FC-DRIVERCHARGE: a fee the driver made up, a demand for extra payment, a transfer outside the app; Jasper, 2026-10-14, open item D40 (b)). As FRD-02 says for the rider's signal, a fraud signal never changes the outcome (GEN-R03); it is shown to the reviewer only, not to the parties, and requires approval (AUTH-02 trigger 2). A human decides any consequence.</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -7064,13 +7064,15 @@
       <c r="J86" s="5" t="inlineStr">
         <is>
           <t>1) [RYDE_POLICY] RYDE-33362721809049 'Driver Performance and Community Standards' (2026-04-10): "5. Remaining stationary and uncontactable after accepting a ride to trigger cancellation or waiting fees"
-2) [RYDE_POLICY] RYDE-33362721809049 'Driver Performance and Community Standards' (2026-04-10): "8. Abuse of Cancellation and Waiting Fee Policy"</t>
+2) [RYDE_POLICY] RYDE-33362721809049 'Driver Performance and Community Standards' (2026-04-10): "8. Abuse of Cancellation and Waiting Fee Policy"
+3) [RYDE_POLICY] RYDE-33362721809049 'Driver Performance and Community Standards' (2026-04-10): "Drivers who overcharge riders and/or complete the trip without the rider onboard." (Community standards, 'Fraudulent Activity': the basis for the signal on a charge the driver made up (D40 (b)).)</t>
         </is>
       </c>
       <c r="K86" s="5" t="inlineStr">
         <is>
           <t>1) 逐字核对通过
-2) 逐字核对通过</t>
+2) 逐字核对通过
+3) 逐字核对通过</t>
         </is>
       </c>
       <c r="L86" s="12" t="inlineStr">
@@ -10923,7 +10925,7 @@
       </c>
       <c r="L43" s="2" t="n"/>
     </row>
-    <row r="44" ht="272" customHeight="1">
+    <row r="44" ht="164" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
           <t>shared</t>
@@ -10961,12 +10963,12 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>20; 100</t>
+          <t>25; 100</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>50 m allows for GPS error near tall buildings. The low end of the plausible range is 20 m (Jasper, 2026-10-14, open item D39 (g)): it sits above ordinary phone GPS error, so jitter around a parked car does not count as being away at the low end. Reasons: GPS-enabled smartphones are typically accurate to about 4.9 m under open sky and worse near buildings, bridges and trees (gps.gov, 'GPS Accuracy'); a smartphone study in a Hong Kong urban canyon, a dense high-rise setting, reports a mean error of about 14.5 m for standard positioning (arXiv 2109.00683, 'Time-correlated Window Carrier-phase Aided GNSS Positioning Using Factor Graph Optimization for Urban Positioning'). Both are paraphrased from search results: the pages could not be fetched from the build environment, so they are not in kb/sources. The organizer's auto-arrival check uses 10 m ('Driver GPS within 10m of pickup point.'), below that error, so it was the low end only until 2026-10-14. FairRyde's choice, D.</t>
+          <t>50 m allows for GPS error near tall buildings. The low end of the plausible range is 25 m (Jasper, 2026-10-14, open item D39 (g)). FairRyde's design reason, with no outside source: the GPS position of a car parked near tall buildings drifts while the car stands still, so at the low end that drift around a parked car must not count as being away. The organizer's auto-arrival check uses 10 m ('Driver GPS within 10m of pickup point.'); it is a check for arriving, not a tolerance for drift, so it is no longer the low end. FairRyde's choice, D.</t>
         </is>
       </c>
       <c r="L44" s="2" t="n"/>
@@ -13064,7 +13066,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="69.5" customHeight="1">
+    <row r="23" ht="110" customHeight="1">
       <c r="A23" s="5" t="inlineStr"/>
       <c r="B23" s="5" t="inlineStr"/>
       <c r="C23" s="5" t="inlineStr"/>
@@ -13085,7 +13087,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Safety content anywhere, judged by meaning (violence or threats, sexual misconduct, abuse or harassment of any kind, being held, being put in danger such as an unsafe drop-off, an accident or injury, discrimination, a crime), creates an SE claim (S0 or S1); unclear text counts as safety content; rudeness alone is feedback</t>
+          <t>Safety content anywhere, judged by meaning (violence or threats, sexual misconduct, abuse or harassment of any kind, being held, being put in danger such as an unsafe drop-off, an accident or injury, discrimination, a crime), creates an SE claim (S0 or S1); unclear text counts as safety content; rudeness alone is feedback; a complaint that mentions discrimination sends the whole case to a person with the case file only, no recommendation on any claim (a contested fee is a secondary claim in the file)</t>
         </is>
       </c>
     </row>
@@ -15611,7 +15613,7 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="29" customHeight="1">
+    <row r="124" ht="56" customHeight="1">
       <c r="A124" s="5" t="inlineStr"/>
       <c r="B124" s="5" t="inlineStr"/>
       <c r="C124" s="5" t="inlineStr"/>
@@ -15628,7 +15630,7 @@
       <c r="H124" s="5" t="inlineStr"/>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>Neutral summary for the reviewer; no credibility finding, no penalty</t>
+          <t>Neutral summary for the reviewer; no credibility finding, no penalty; when the complaint mentions discrimination, the case file only, with no recommendation on any claim and no interim measure (SE-R01)</t>
         </is>
       </c>
     </row>
@@ -20992,12 +20994,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>50 · [20, 100] · D</t>
+          <t>50 · [25, 100] · D</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>20 -&gt; UPHOLD (R8)</t>
+          <t>25 -&gt; UPHOLD (R8)</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -21798,7 +21800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I132"/>
+  <dimension ref="A1:I134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -24010,7 +24012,7 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>decisive: CW-F03B (the other reading (wait counted from the anchor, regardless of GPS) gives UPHOLD); CW-R06 (outcome changes when TS_TOLERANCE_S moves within [5, 60]); CW-F04B (outcome changes when TS_TOLERANCE_S moves within [5, 60]); CW-F06 (outcome changes when TS_TOLERANCE_S moves within [5, 60]); CW-F04B (outcome changes when ARRIVAL_GEOFENCE_M moves within [20, 100]); fraud signal on RIDER (3 of 4 past disputes rejected; platform flag: flagged_for_frequent_late_cancellations) (symmetric trigger; the detail is for the reviewer, not for the parties)</t>
+          <t>decisive: CW-F03B (the other reading (wait counted from the anchor, regardless of GPS) gives UPHOLD); CW-R06 (outcome changes when TS_TOLERANCE_S moves within [5, 60]); CW-F04B (outcome changes when TS_TOLERANCE_S moves within [5, 60]); CW-F06 (outcome changes when TS_TOLERANCE_S moves within [5, 60]); CW-F04B (outcome changes when ARRIVAL_GEOFENCE_M moves within [25, 100]); fraud signal on RIDER (3 of 4 past disputes rejected; platform flag: flagged_for_frequent_late_cancellations) (symmetric trigger; the detail is for the reviewer, not for the parties)</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr"/>
@@ -26198,7 +26200,7 @@
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>V06 with pings 3 m from the pin and one 25 m away: inside the 50 m area, but at the radius's 20 m low end it is an outlier, so the uphold would rest on FairRyde's logic (D29, radius part): approval</t>
+          <t>V06 with pings 3 m from the pin and one 30 m away: inside the 50 m area, but at the radius's 25 m low end it is an outlier, so the uphold would rest on FairRyde's logic (D29, radius part): approval</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
@@ -26223,7 +26225,7 @@
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>decisive: CW-F04B (the ruling would rest on a decision-table row rated C or D when ARRIVAL_GEOFENCE_M moves within [20, 100]); fee upheld, and FairRyde's own GPS logic would decide it with ARRIVAL_GEOFENCE_M at an end of its plausible range (CW-F04B, D29)</t>
+          <t>decisive: CW-F04B (the ruling would rest on a decision-table row rated C or D when ARRIVAL_GEOFENCE_M moves within [25, 100]); fee upheld, and FairRyde's own GPS logic would decide it with ARRIVAL_GEOFENCE_M at an end of its plausible range (CW-F04B, D29)</t>
         </is>
       </c>
       <c r="H111" s="7" t="inlineStr"/>
@@ -26241,7 +26243,7 @@
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>as V99 with the far ping 15 m away: ordinary GPS error, inside the radius even at its 20 m low end (Jasper, 2026-10-14, D39 (g)), so the uphold rests on the pings alone: automatic</t>
+          <t>as V99 with the far ping 20 m away: GPS drift around a parked car, inside the radius even at its 25 m low end (Jasper, 2026-10-14, D39 (g)), so the uphold rests on the pings alone: automatic</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
@@ -26495,7 +26497,7 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="191" customHeight="1">
+    <row r="118" ht="69.5" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
         <is>
           <t>V106</t>
@@ -26508,27 +26510,23 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>tier: HUMAN; gates: G4</t>
+          <t>tier: HUMAN; gates: G4; outcome: ESCALATE_HUMAN; reasons: SE-R-HUMAN-DECIDES; row: ; triggers: mentions discrimination</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>outcome: UPHOLD; row: R8; tier: HUMAN; reasons: CW-R-NOSHOW-VALID; CW-R-PIN-AMBIGUOUS; profile: organizer_case; C: 0.689</t>
+          <t>outcome: ESCALATE_HUMAN; tier: HUMAN; reasons: SE-R-HUMAN-DECIDES; profile: organizer_case</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>BOOKING_TYPE_INFERRED; BOUNDARY_MARGIN; MARGIN_WITHIN_SPREAD; NO_RIDER_EVIDENCE; PIN_VENUE_MISMATCH; FRAUD_SIGNAL; GENERIC_ASSUMPTION_USED</t>
-        </is>
-      </c>
-      <c r="F118" s="7" t="inlineStr">
-        <is>
-          <t>CW-F04B</t>
-        </is>
-      </c>
+          <t>BOOKING_TYPE_INFERRED; BOUNDARY_MARGIN; MARGIN_WITHIN_SPREAD; NO_RIDER_EVIDENCE; PIN_VENUE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr"/>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>decisive: CW-F04B (outcome changes when PING_MAX_GAP_S moves within [60, 420]); fraud signal on RIDER (3 of 4 past disputes rejected; platform flag: flagged_for_frequent_late_cancellations) (symmetric trigger; the detail is for the reviewer, not for the parties); fee upheld, and FairRyde's own GPS logic would decide it with PING_MAX_GAP_S at an end of its plausible range (CW-F04B, D29); margin +0 s within the boundary band, and the records disagree by up to 10 s; fee upheld, pin far from Tiong Bahru Plaza and the rider says they were there</t>
+          <t>the complaint mentions discrimination: the whole case goes to a person with the case file only (CLS-01, SE-R01)</t>
         </is>
       </c>
       <c r="H118" s="7" t="inlineStr">
@@ -26966,35 +26964,117 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="n"/>
-      <c r="B131" s="2" t="n"/>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n"/>
-      <c r="E131" s="2" t="n"/>
-      <c r="F131" s="2" t="n"/>
-      <c r="G131" s="2" t="n"/>
-      <c r="H131" s="2" t="n"/>
-      <c r="I131" s="2" t="n"/>
-    </row>
-    <row r="132" ht="29" customHeight="1">
-      <c r="A132" s="10" t="inlineStr">
+    <row r="131" ht="96.5" customHeight="1">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>V119</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>a clean automatic uphold, but the rider's message says the driver canceled because of the rider's ethnicity: no proposed outcome, the whole case to a person, the fee a secondary claim (CLS-01, SE-R01)</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>outcome: ESCALATE_HUMAN; reasons: SE-R-HUMAN-DECIDES; row: ; tier: HUMAN; gates: G4</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>outcome: ESCALATE_HUMAN; tier: HUMAN; reasons: SE-R-HUMAN-DECIDES; profile: organizer_case</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>BOOKING_TYPE_INFERRED; NO_RIDER_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr"/>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>the complaint mentions discrimination: the whole case goes to a person with the case file only (CLS-01, SE-R01)</t>
+        </is>
+      </c>
+      <c r="H131" s="7" t="inlineStr">
+        <is>
+          <t>G4 safety content</t>
+        </is>
+      </c>
+      <c r="I131" s="7" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="56" customHeight="1">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>V120</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>a rider cancellation whose description mentions discrimination: reclassified, and the whole case to a person</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>reclassified: CW-RIDERCANCEL; tier: HUMAN; gates: G4</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>tier: HUMAN; reasons: ; profile: organizer_case; reclassified: CW-RIDERCANCEL</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr"/>
+      <c r="F132" s="7" t="inlineStr"/>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>the complaint mentions discrimination: the whole case goes to a person with the case file only (CLS-01, SE-R01)</t>
+        </is>
+      </c>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
+          <t>G4 safety content</t>
+        </is>
+      </c>
+      <c r="I132" s="7" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n"/>
+      <c r="B133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n"/>
+      <c r="E133" s="2" t="n"/>
+      <c r="F133" s="2" t="n"/>
+      <c r="G133" s="2" t="n"/>
+      <c r="H133" s="2" t="n"/>
+      <c r="I133" s="2" t="n"/>
+    </row>
+    <row r="134" ht="29" customHeight="1">
+      <c r="A134" s="10" t="inlineStr">
         <is>
           <t>覆盖：决策表行 R1, R2, R3, R4, R5, R6, R7, R8, R9, R10, R11；自治等级 APPROVE, AUTO, HUMAN, n/a (reclassified to CW-OTHER), n/a (reclassified to CW-RIDERCANCEL)；另有改判（MAT-04 超期、META-02 生效日期、CW-R00 RydeTAXI）和重新分类（V10）。</t>
         </is>
       </c>
-      <c r="B132" s="2" t="n"/>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n"/>
-      <c r="E132" s="2" t="n"/>
-      <c r="F132" s="2" t="n"/>
-      <c r="G132" s="2" t="n"/>
-      <c r="H132" s="2" t="n"/>
-      <c r="I132" s="2" t="n"/>
+      <c r="B134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n"/>
+      <c r="E134" s="2" t="n"/>
+      <c r="F134" s="2" t="n"/>
+      <c r="G134" s="2" t="n"/>
+      <c r="H134" s="2" t="n"/>
+      <c r="I134" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A132:H132"/>
+    <mergeCell ref="A134:H134"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -30885,7 +30965,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>done; implemented in A3 (2026-10-14): CW-F04 keeps Ryde's condition (B) and the new rule CW-F04B holds FairRyde's GPS presence logic (D) with its finding F-GPS-LOGIC, true when the logic and not the pings alone makes the driver count as arrived and present (a ping set aside that could change the presence or the arrival, an outside ping in the window not counted as leaving, a later GPS confirmation, SPARSE or GPS_AMBIGUOUS). No-show fees: DT-CW-NOSHOW input gps_logic_decides; R8 (B) needs it false, the new row R11 (D) is the same uphold when it is true, so the row is decisive and the fee needs approval; the engine also lists the trigger. The ping-gap and radius part: a CW-F04B parameter that would make F-GPS-LOGIC true at an end of its plausible range moves a no-show uphold onto R9 or R11, which decisive_definition clause 2 counts as decisive; for waiting fees (no decision table, D31) AUTH-02 trigger 12 and CW-F04B's text state both parts (check round 1 found the parameter part missing for waiting fees, SG-1 and ADV-1), pointed to from PB-CW-WAITING step 5. The decisive parameter is reported against CW-F04B, or CW-R06 when only the arrival finding moves. The set-aside pings that count are those that could change the presence (in the window) or the arrival (one that would otherwise have been CW-R06's moment ping; with the platform check, only one at or after the indication), check rounds 1 and 2. Check round 2 also made GPS_AMBIGUOUS cover both window edges (ADV2-1, CRITICAL): a driver last seen at the pin more than TS_TOLERANCE_S before the window end and next seen away before the cancellation, and a window that starts after the arrival while the driver was last seen away. Tests: V94 to V103 and ten re-rated variants, an A3 rule-card check, and a fuzz invariant (no automatic uphold with F-GPS-LOGIC true, an outside ping in the window, or a first ping away after the window end that follows a last inside ping more than TS_TOLERANCE_S before the window end). Tier report: validation/build_checks/A3/01b_tier_report.md (DISP-002 and E01 to E04 unchanged). Cost, for Jasper (check round 1, ADV-2): the radius part makes a clean uphold with ordinary GPS jitter (a ping between 10 and 50 m from the pin) go to approval, because at the radius's 10 m low end that ping would be set aside; see D39 (g). Jasper, 2026-10-14: the radius's plausible range starts at 20 m, above ordinary phone GPS error (reasons in reference_data.yaml); a ping between 20 and 50 m from the pin still sends the uphold to approval. In the jitter simulation (600 clean upholds, seed 5) automatic upholds go from 29 back to 204 (A2: 235); V99 and V99B pin both sides.</t>
+          <t>done; implemented in A3 (2026-10-14): CW-F04 keeps Ryde's condition (B) and the new rule CW-F04B holds FairRyde's GPS presence logic (D) with its finding F-GPS-LOGIC, true when the logic and not the pings alone makes the driver count as arrived and present (a ping set aside that could change the presence or the arrival, an outside ping in the window not counted as leaving, a later GPS confirmation, SPARSE or GPS_AMBIGUOUS). No-show fees: DT-CW-NOSHOW input gps_logic_decides; R8 (B) needs it false, the new row R11 (D) is the same uphold when it is true, so the row is decisive and the fee needs approval; the engine also lists the trigger. The ping-gap and radius part: a CW-F04B parameter that would make F-GPS-LOGIC true at an end of its plausible range moves a no-show uphold onto R9 or R11, which decisive_definition clause 2 counts as decisive; for waiting fees (no decision table, D31) AUTH-02 trigger 12 and CW-F04B's text state both parts (check round 1 found the parameter part missing for waiting fees, SG-1 and ADV-1), pointed to from PB-CW-WAITING step 5. The decisive parameter is reported against CW-F04B, or CW-R06 when only the arrival finding moves. The set-aside pings that count are those that could change the presence (in the window) or the arrival (one that would otherwise have been CW-R06's moment ping; with the platform check, only one at or after the indication), check rounds 1 and 2. Check round 2 also made GPS_AMBIGUOUS cover both window edges (ADV2-1, CRITICAL): a driver last seen at the pin more than TS_TOLERANCE_S before the window end and next seen away before the cancellation, and a window that starts after the arrival while the driver was last seen away. Tests: V94 to V103 and ten re-rated variants, an A3 rule-card check, and a fuzz invariant (no automatic uphold with F-GPS-LOGIC true, an outside ping in the window, or a first ping away after the window end that follows a last inside ping more than TS_TOLERANCE_S before the window end). Tier report: validation/build_checks/A3/01b_tier_report.md (DISP-002 and E01 to E04 unchanged). Cost, for Jasper (check round 1, ADV-2): the radius part makes a clean uphold with ordinary GPS jitter (a ping between 10 and 50 m from the pin) go to approval, because at the radius's 10 m low end that ping would be set aside; see D39 (g). Jasper, 2026-10-14: the radius's plausible range starts at 25 m, so GPS drift around a car parked near tall buildings does not count as being away at the low end (FairRyde's design reason, no outside source, credibility D; reference_data.yaml); a ping between 25 and 50 m from the pin still sends the uphold to approval. In the jitter simulation (600 clean upholds, seed 5) automatic upholds go from 29 back to 347 (A2: 235); V99 (30 m, approval) and V99B (20 m, automatic) pin both sides.</t>
         </is>
       </c>
     </row>
@@ -31155,7 +31235,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>done in A3. Judgments for Jasper, not changed: (a) CW-R06 stays B: its FairRyde parts (the outlier step, the later confirmation, CONTESTED, UNKNOWN) are rated D in the rules they belong to (CW-F04B, CW-F03B, GEN-R02, GEN-R01); every row whose ruling rests on them is D (R2, R3, R9, R11), except a short-wait waiver (R6, A) that rests on a later confirmation, which CW-F03B's start test sends to approval when another reading changes it; reading Ryde's GPS condition at the moment of the arrival through the last remaining ping from PING_MAX_GAP_S before to TS_TOLERANCE_S after it is counted as Ryde's condition, with its look-back, tolerance and radius as D parameters tested by the sensitivity test; (b) FC-R01 stays B: recording the deviation as conduct information and opening the FC-TOLL claim are FairRyde's (D) but set no amount and add no condition to the no-refund finding; (c) AUTH-03 stays B: a human deciding (not only approving) safety matters is stricter than the IMDA guidance and only sends more cases to people; (d) R1 and R4 stay B: setting a ping aside only removes evidence that the driver was away, so a FALSE arrival or LEFT found with the logic also holds on the pings alone, except a data error (gate G1, approval); (e) CW-R08 would be C again with a local source for its 'not moving' ground (Grab's cancellation page) and, since A4, for its advance-booking ETA; (f) FX9 leftovers seen in the census, done in A4: CW-F02B cites the 2024 driver page RYDE-20244064619161, and CW-R08 defines the assignment ETA of an advance booking (see D40). Check round 1 (A3) added: (a') the reviewers note that 'delegated' is the builder's category, not FX4's wording; if Jasper reads FX4 literally, CW-R06 is D, R1 and R8 become D, and every no-show uphold and every R1 waiver goes to approval; the alternative is to split CW-R06 as CW-F04 was; (b') and (c') are the same kind of judgment (a FairRyde step in the conclusion of FC-R01; a stricter-than-source reading in AUTH-03); (g) the radius part of D29 (ADV-2): with pings 3 m from the pin and one at 15 m, V99 now goes to approval (it was automatic in A2); a reviewer's simulation of 600 clean upholds on the round 1 draft (parked 0 to 25 m from the pin, normal jitter) found automatic upholds falling from 38% to 5% (198 of the 201 moved cases through ARRIVAL_GEOFENCE_M's 10 m low end, 3 through TS_TOLERANCE_S); the builder's run (validation/build_checks/A3/jitter_sim.py) gives 235 to 29 of 600, every moved case through the radius; options: keep it (D29 as written), exempt the radius from the row-move part of clause 2, or raise the radius's low end above the platform's 10 m check; (h) the toll engine does not mark FC-R07's refund (now D) as a generic assumption: META-05 needs a decisive rule and decisive_definition makes a D outcome rule decisive only through a decision-table row; every FC-R07 refund already needs approval because of the fraud signal; (i) pre-existing engine defect fixed in A3 (ADV-3): pings were sorted by their timestamp text, so pings written with another UTC offset were read out of order (a departure became an outlier); they are now sorted by instant (V98), and read on the trip record's clock. Check round 2 (A3) added: (j) pre-existing, not fixed: a GPS timestamp without a UTC offset makes the engine stop with an error (no ruling, no tier), so such a case reaches no automatic ruling but also no routing; normalizing it needs a data-quality rule (DQ-03 or DQ-04); (k) frozen area (D34), not fixed: the reader's answers_question orders the driver's messages by their timestamp text, the defect fixed for GPS pings in (i); (l) the fuzz generator makes no advance bookings; V101 and V103 pin the advance-booking edges. Jasper's decisions of 2026-10-14: (a), (b) and (c) CW-R06, FC-R01 and AUTH-03 stay B as they are; (g) the radius's low end is raised to 20 m, above ordinary phone GPS error (D29; ARRIVAL_GEOFENCE_M in reference_data.yaml, credibility D); the other points stay as recorded.</t>
+          <t>done in A3. Judgments for Jasper, not changed: (a) CW-R06 stays B: its FairRyde parts (the outlier step, the later confirmation, CONTESTED, UNKNOWN) are rated D in the rules they belong to (CW-F04B, CW-F03B, GEN-R02, GEN-R01); every row whose ruling rests on them is D (R2, R3, R9, R11), except a short-wait waiver (R6, A) that rests on a later confirmation, which CW-F03B's start test sends to approval when another reading changes it; reading Ryde's GPS condition at the moment of the arrival through the last remaining ping from PING_MAX_GAP_S before to TS_TOLERANCE_S after it is counted as Ryde's condition, with its look-back, tolerance and radius as D parameters tested by the sensitivity test; (b) FC-R01 stays B: recording the deviation as conduct information and opening the FC-TOLL claim are FairRyde's (D) but set no amount and add no condition to the no-refund finding; (c) AUTH-03 stays B: a human deciding (not only approving) safety matters is stricter than the IMDA guidance and only sends more cases to people; (d) R1 and R4 stay B: setting a ping aside only removes evidence that the driver was away, so a FALSE arrival or LEFT found with the logic also holds on the pings alone, except a data error (gate G1, approval); (e) CW-R08 would be C again with a local source for its 'not moving' ground (Grab's cancellation page) and, since A4, for its advance-booking ETA; (f) FX9 leftovers seen in the census, done in A4: CW-F02B cites the 2024 driver page RYDE-20244064619161, and CW-R08 defines the assignment ETA of an advance booking (see D40). Check round 1 (A3) added: (a') the reviewers note that 'delegated' is the builder's category, not FX4's wording; if Jasper reads FX4 literally, CW-R06 is D, R1 and R8 become D, and every no-show uphold and every R1 waiver goes to approval; the alternative is to split CW-R06 as CW-F04 was; (b') and (c') are the same kind of judgment (a FairRyde step in the conclusion of FC-R01; a stricter-than-source reading in AUTH-03); (g) the radius part of D29 (ADV-2): with pings 3 m from the pin and one at 15 m, V99 now goes to approval (it was automatic in A2); a reviewer's simulation of 600 clean upholds on the round 1 draft (parked 0 to 25 m from the pin, normal jitter) found automatic upholds falling from 38% to 5% (198 of the 201 moved cases through ARRIVAL_GEOFENCE_M's 10 m low end, 3 through TS_TOLERANCE_S); the builder's run (validation/build_checks/A3/jitter_sim.py) gives 235 to 29 of 600, every moved case through the radius; options: keep it (D29 as written), exempt the radius from the row-move part of clause 2, or raise the radius's low end above the platform's 10 m check; (h) the toll engine does not mark FC-R07's refund (now D) as a generic assumption: META-05 needs a decisive rule and decisive_definition makes a D outcome rule decisive only through a decision-table row; every FC-R07 refund already needs approval because of the fraud signal; (i) pre-existing engine defect fixed in A3 (ADV-3): pings were sorted by their timestamp text, so pings written with another UTC offset were read out of order (a departure became an outlier); they are now sorted by instant (V98), and read on the trip record's clock. Check round 2 (A3) added: (j) pre-existing, not fixed: a GPS timestamp without a UTC offset makes the engine stop with an error (no ruling, no tier), so such a case reaches no automatic ruling but also no routing; normalizing it needs a data-quality rule (DQ-03 or DQ-04); (k) frozen area (D34), not fixed: the reader's answers_question orders the driver's messages by their timestamp text, the defect fixed for GPS pings in (i); (l) the fuzz generator makes no advance bookings; V101 and V103 pin the advance-booking edges. Jasper's decisions of 2026-10-14: (a), (b) and (c) CW-R06, FC-R01 and AUTH-03 stay B as they are; (g) the radius's low end is raised to 25 m, FairRyde's design reason being GPS drift around a car parked near tall buildings (D29; ARRIVAL_GEOFENCE_M in reference_data.yaml, credibility D); the other points stay as recorded.</t>
         </is>
       </c>
     </row>
@@ -31182,7 +31262,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>done in A4. For Jasper: (a) the reference engine's safety check is still a list (SAFETY_PATTERNS, whole-word patterns since check round 1, erring toward safety); it misses paraphrases that use none of its patterns (a reviewer found 22 of 22 such texts missed), so it is a test stand-in, not the classifier; the definition is for the LLM classifier, and validation round 2's taxonomy texts test it; (b) FC-FAREMISMATCH and FC-DRIVERCHARGE are BACKLOG (a person decides); a driver who made up a charge may also deserve a fraud signal (FRD-01 does not cover it yet); (c) discrimination now makes a claim SE-CONDUCT and primary even when the complaint is mainly about a fee (C05's discriminatory refusal is now a safety claim, not CW-DRIVERNOSHOW); (d) the case data has no field for several drop-offs in the organizer's sample (trip_data.stops is a data gap). Check round 1 (A4) added: (e) CLS-01 now counts abuse or harassment of any kind (insults, slurs, personal questions, comments on appearance, personal contact after the trip) as safety content, following Ryde's Code of Conduct item 5, and keeps only an unfriendly manner, a raised voice or a curt reply as feedback; where that line lies is FairRyde's design and Jasper's call; (f) CLS-01 no longer names a rider under the influence (Ryde's text is about the driver), and being stranded counts only when the driver made the passenger leave or left them behind, so a cleaning claim about a drunk rider or a cancellation complaint saying 'stranded' is not safety content by those examples alone; (g) the engine records no secondary EX-FEEDBACK claim for a rudeness complaint (V107); the claim splitting of CLS-02 is for the LLM classifier; (h) FC-R12 for a changed itinerary now applies only when the recommended route can change the amount, so a RydeSEND claim or one with no ERP passed or charged keeps its automatic ruling; (i) a reclassified case with safety content now goes to a person (gate G4), as CLS-01 requires; (j) safety_termination does not name the party, so CLS-06 takes the party from the other records. Check round 2 (A4) added: (k) a CW-R08 waiver can be automatic: CW-R08 is D, but decisive_definition makes a D outcome rule decisive only through a decision-table row and CW-RIDERCANCEL has no table (the same gap as D39 (h) for FC-R07); A4 narrowed the 'not moving' ground for advance bookings (an early driver waiting nearby is not a ground), and whether every CW-R08 waiver should need approval is Jasper's call; (l) the reference engines read the trip record's wording with patterns (canceling_party in engine_noshow.py, itinerary_change in engine_toll.py); a record they cannot read counts as disagreeing or as a possible change, so it goes to a person, never to an automatic ruling. Jasper's decisions of 2026-10-14: (a) the engine's safety pattern list and (d) the missing field for several drop-offs (trip_data.stops) are known limitations of v0.2; (e) the line between rudeness and abuse stays as A4 drew it; (k) every CW-R08 waiver needs approval, in line with D29 (AUTH-02 trigger 13, CW-R08, PB-CW-RIDERCANCEL step 5).</t>
+          <t>done in A4. For Jasper: (a) the reference engine's safety check is still a list (SAFETY_PATTERNS, whole-word patterns since check round 1, erring toward safety); it misses paraphrases that use none of its patterns (a reviewer found 22 of 22 such texts missed), so it is a test stand-in, not the classifier; the definition is for the LLM classifier, and validation round 2's taxonomy texts test it; (b) FC-FAREMISMATCH and FC-DRIVERCHARGE are BACKLOG (a person decides); a driver who made up a charge may also deserve a fraud signal (FRD-01 does not cover it yet); (c) discrimination now makes a claim SE-CONDUCT and primary even when the complaint is mainly about a fee (C05's discriminatory refusal is now a safety claim, not CW-DRIVERNOSHOW); (d) the case data has no field for several drop-offs in the organizer's sample (trip_data.stops is a data gap). Check round 1 (A4) added: (e) CLS-01 now counts abuse or harassment of any kind (insults, slurs, personal questions, comments on appearance, personal contact after the trip) as safety content, following Ryde's Code of Conduct item 5, and keeps only an unfriendly manner, a raised voice or a curt reply as feedback; where that line lies is FairRyde's design and Jasper's call; (f) CLS-01 no longer names a rider under the influence (Ryde's text is about the driver), and being stranded counts only when the driver made the passenger leave or left them behind, so a cleaning claim about a drunk rider or a cancellation complaint saying 'stranded' is not safety content by those examples alone; (g) the engine records no secondary EX-FEEDBACK claim for a rudeness complaint (V107); the claim splitting of CLS-02 is for the LLM classifier; (h) FC-R12 for a changed itinerary now applies only when the recommended route can change the amount, so a RydeSEND claim or one with no ERP passed or charged keeps its automatic ruling; (i) a reclassified case with safety content now goes to a person (gate G4), as CLS-01 requires; (j) safety_termination does not name the party, so CLS-06 takes the party from the other records. Check round 2 (A4) added: (k) a CW-R08 waiver can be automatic: CW-R08 is D, but decisive_definition makes a D outcome rule decisive only through a decision-table row and CW-RIDERCANCEL has no table (the same gap as D39 (h) for FC-R07); A4 narrowed the 'not moving' ground for advance bookings (an early driver waiting nearby is not a ground), and whether every CW-R08 waiver should need approval is Jasper's call; (l) the reference engines read the trip record's wording with patterns (canceling_party in engine_noshow.py, itinerary_change in engine_toll.py); a record they cannot read counts as disagreeing or as a possible change, so it goes to a person, never to an automatic ruling. Jasper's decisions of 2026-10-14: (a) the engine's safety pattern list and (d) the missing field for several drop-offs (trip_data.stops) are known limitations of v0.2; (e) the line between rudeness and abuse stays as A4 drew it; (k) every CW-R08 waiver needs approval, in line with D29 (AUTH-02 trigger 13, CW-R08, PB-CW-RIDERCANCEL step 5); (b) a charge the driver made up (FC-DRIVERCHARGE) raises a fraud signal against the driver (FRD-01): like FRD-02's signal it never changes the outcome and is shown to the reviewer only; (c) a complaint that mentions discrimination is always safety content and the whole case goes to a person: FairRyde prepares the case file only and proposes no outcome, amount or measure on any claim, and a contested fee is a secondary claim in the file (CLS-01, CLS-02, SE-R01, PB-INTAKE step 2, PB-TRIAGE-HUMAN step 6; engine: V106, V119, V120).</t>
         </is>
       </c>
     </row>
@@ -32030,7 +32110,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>90 条规则，各有来源、可信度（A 26、B 9、C 1、D 54）和模式（HARD 75、READ 9、HARD+READ 6）；148 条引文由脚本逐字核对，0 条不符；Ryde 页面之间的矛盾按条款记录，矛盾一方的条款不能支撑 A 级。</t>
+          <t>90 条规则，各有来源、可信度（A 26、B 9、C 1、D 54）和模式（HARD 75、READ 9、HARD+READ 6）；149 条引文由脚本逐字核对，0 条不符；Ryde 页面之间的矛盾按条款记录，矛盾一方的条款不能支撑 A 级。</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -36141,7 +36221,7 @@
       </c>
       <c r="O31" s="11" t="inlineStr"/>
     </row>
-    <row r="32" ht="353" customHeight="1">
+    <row r="32" ht="360" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
           <t>TX-CASE</t>
@@ -36175,7 +36255,7 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>A rider or driver reports behavior by the other party toward a person that threatens their safety or that Ryde lists as misconduct between drivers and passengers (Code of Conduct item 5, community standards): physical assault or an attempt, verbal or physical sexual harassment, unwanted sexual advances, threats and intimidation, kidnapping or being held against one's will, abuse or harassment of any kind (insults, slurs, overly personal questions, comments on appearance, personal contact after the trip), and discrimination because of race, ethnicity, religion, nationality, disability or a similar ground (including a refusal or a canceled trip for that reason). Rudeness alone (an unfriendly or impatient manner, a raised voice, a curt reply) with no abuse, threat or discrimination is feedback (EX-FEEDBACK).</t>
+          <t>A rider or driver reports behavior by the other party toward a person that threatens their safety or that Ryde lists as misconduct between drivers and passengers (Code of Conduct item 5, community standards): physical assault or an attempt, verbal or physical sexual harassment, unwanted sexual advances, threats and intimidation, kidnapping or being held against one's will, abuse or harassment of any kind (insults, slurs, overly personal questions, comments on appearance, personal contact after the trip), and discrimination because of race, ethnicity, religion, nationality, disability or a similar ground (including a refusal or a canceled trip for that reason). Rudeness alone (an unfriendly or impatient manner, a raised voice, a curt reply) with no abuse, threat or discrimination is feedback (EX-FEEDBACK). A complaint that mentions discrimination sends the whole case to a person with the case file only, no recommendation (CLS-01, SE-R01).</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
